--- a/notebooks/cell_number_accounting.xlsx
+++ b/notebooks/cell_number_accounting.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="86">
   <si>
     <t>Adipocytes</t>
   </si>
@@ -192,6 +192,30 @@
     <t>Macs</t>
   </si>
   <si>
+    <t>CAF.Coagulation</t>
+  </si>
+  <si>
+    <t>CAF.Fibrosis</t>
+  </si>
+  <si>
+    <t>CAF.Interferon</t>
+  </si>
+  <si>
+    <t>CAF.Lipid</t>
+  </si>
+  <si>
+    <t>CAF.MHCII</t>
+  </si>
+  <si>
+    <t>CAF.Myo-TGFB</t>
+  </si>
+  <si>
+    <t>CAF.Myogenesis</t>
+  </si>
+  <si>
+    <t>CAF.Pericyte-like</t>
+  </si>
+  <si>
     <t>CD8T.Cytotoxic</t>
   </si>
   <si>
@@ -199,6 +223,24 @@
   </si>
   <si>
     <t>CD8T.Naive</t>
+  </si>
+  <si>
+    <t>Endothelial.Adipogenesis-I</t>
+  </si>
+  <si>
+    <t>Endothelial.EBV</t>
+  </si>
+  <si>
+    <t>Endothelial.EMT-I</t>
+  </si>
+  <si>
+    <t>Endothelial.HEV</t>
+  </si>
+  <si>
+    <t>Endothelial.Hypoxia</t>
+  </si>
+  <si>
+    <t>Endothelial.Notch-signaling</t>
   </si>
   <si>
     <t>Macs.Adhesion</t>
@@ -4557,10 +4599,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AA42"/>
+  <dimension ref="A1:AM42"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:27">
+    <row r="1" spans="1:39">
       <c r="A1" s="1" t="s">
         <v>13</v>
       </c>
@@ -4571,79 +4613,115 @@
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>2</v>
+        <v>58</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J1" s="1" t="s">
+      <c r="M1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="V1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="L1" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q1" s="1" t="s">
+      <c r="X1" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="AC1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="AG1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="V1" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="2" spans="1:27">
+      <c r="AH1" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="AI1" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="AJ1" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="AK1" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="AL1" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="AM1" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="2" spans="1:39">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
@@ -4654,79 +4732,115 @@
         <v>28</v>
       </c>
       <c r="D2">
-        <v>1728</v>
+        <v>1298</v>
       </c>
       <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>14</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
+      </c>
+      <c r="H2">
+        <v>193</v>
+      </c>
+      <c r="I2">
+        <v>5</v>
+      </c>
+      <c r="J2">
+        <v>119</v>
+      </c>
+      <c r="K2">
+        <v>95</v>
+      </c>
+      <c r="L2">
         <v>24</v>
       </c>
-      <c r="F2">
+      <c r="M2">
         <v>72</v>
       </c>
-      <c r="G2">
+      <c r="N2">
         <v>52</v>
       </c>
-      <c r="H2">
+      <c r="O2">
         <v>129</v>
       </c>
-      <c r="I2">
-        <v>214</v>
-      </c>
-      <c r="J2">
+      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2">
+        <v>40</v>
+      </c>
+      <c r="R2">
+        <v>76</v>
+      </c>
+      <c r="S2">
+        <v>16</v>
+      </c>
+      <c r="T2">
+        <v>67</v>
+      </c>
+      <c r="U2">
+        <v>15</v>
+      </c>
+      <c r="V2">
         <v>2900</v>
       </c>
-      <c r="K2">
+      <c r="W2">
         <v>105</v>
       </c>
-      <c r="L2">
+      <c r="X2">
         <v>266</v>
       </c>
-      <c r="M2">
+      <c r="Y2">
         <v>15</v>
       </c>
-      <c r="N2">
+      <c r="Z2">
         <v>41</v>
       </c>
-      <c r="O2">
+      <c r="AA2">
         <v>445</v>
       </c>
-      <c r="P2">
+      <c r="AB2">
         <v>44</v>
       </c>
-      <c r="Q2">
+      <c r="AC2">
         <v>3</v>
       </c>
-      <c r="R2">
+      <c r="AD2">
         <v>117</v>
       </c>
-      <c r="S2">
+      <c r="AE2">
         <v>105</v>
       </c>
-      <c r="T2">
+      <c r="AF2">
         <v>29</v>
       </c>
-      <c r="U2">
-        <v>1</v>
-      </c>
-      <c r="V2">
+      <c r="AG2">
+        <v>1</v>
+      </c>
+      <c r="AH2">
         <v>1489</v>
       </c>
-      <c r="W2">
+      <c r="AI2">
         <v>1533</v>
       </c>
-      <c r="X2">
+      <c r="AJ2">
         <v>87</v>
       </c>
-      <c r="Y2">
+      <c r="AK2">
         <v>98</v>
       </c>
-      <c r="Z2">
+      <c r="AL2">
         <v>862</v>
       </c>
-      <c r="AA2">
+      <c r="AM2">
         <v>60</v>
       </c>
     </row>
-    <row r="3" spans="1:27">
+    <row r="3" spans="1:39">
       <c r="A3" s="1" t="s">
         <v>15</v>
       </c>
@@ -4737,79 +4851,115 @@
         <v>154</v>
       </c>
       <c r="D3">
-        <v>1344</v>
+        <v>807</v>
       </c>
       <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>43</v>
+      </c>
+      <c r="G3">
+        <v>4</v>
+      </c>
+      <c r="H3">
+        <v>78</v>
+      </c>
+      <c r="I3">
+        <v>14</v>
+      </c>
+      <c r="J3">
+        <v>353</v>
+      </c>
+      <c r="K3">
+        <v>45</v>
+      </c>
+      <c r="L3">
         <v>142</v>
       </c>
-      <c r="F3">
+      <c r="M3">
         <v>863</v>
       </c>
-      <c r="G3">
+      <c r="N3">
         <v>194</v>
       </c>
-      <c r="H3">
+      <c r="O3">
         <v>410</v>
       </c>
-      <c r="I3">
-        <v>72</v>
-      </c>
-      <c r="J3">
+      <c r="P3">
+        <v>0</v>
+      </c>
+      <c r="Q3">
+        <v>6</v>
+      </c>
+      <c r="R3">
+        <v>48</v>
+      </c>
+      <c r="S3">
+        <v>10</v>
+      </c>
+      <c r="T3">
+        <v>4</v>
+      </c>
+      <c r="U3">
+        <v>4</v>
+      </c>
+      <c r="V3">
         <v>553</v>
       </c>
-      <c r="K3">
+      <c r="W3">
         <v>125</v>
       </c>
-      <c r="L3">
+      <c r="X3">
         <v>71</v>
       </c>
-      <c r="M3">
+      <c r="Y3">
         <v>38</v>
       </c>
-      <c r="N3">
+      <c r="Z3">
         <v>130</v>
       </c>
-      <c r="O3">
+      <c r="AA3">
         <v>349</v>
       </c>
-      <c r="P3">
+      <c r="AB3">
         <v>32</v>
       </c>
-      <c r="Q3">
+      <c r="AC3">
         <v>24</v>
       </c>
-      <c r="R3">
+      <c r="AD3">
         <v>70</v>
       </c>
-      <c r="S3">
+      <c r="AE3">
         <v>112</v>
       </c>
-      <c r="T3">
+      <c r="AF3">
         <v>12</v>
       </c>
-      <c r="U3">
-        <v>0</v>
-      </c>
-      <c r="V3">
+      <c r="AG3">
+        <v>0</v>
+      </c>
+      <c r="AH3">
         <v>266</v>
       </c>
-      <c r="W3">
+      <c r="AI3">
         <v>710</v>
       </c>
-      <c r="X3">
+      <c r="AJ3">
         <v>2</v>
       </c>
-      <c r="Y3">
+      <c r="AK3">
         <v>6</v>
       </c>
-      <c r="Z3">
+      <c r="AL3">
         <v>35</v>
       </c>
-      <c r="AA3">
+      <c r="AM3">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:27">
+    <row r="4" spans="1:39">
       <c r="A4" s="1" t="s">
         <v>16</v>
       </c>
@@ -4820,79 +4970,115 @@
         <v>146</v>
       </c>
       <c r="D4">
-        <v>2319</v>
+        <v>53</v>
       </c>
       <c r="E4">
+        <v>3</v>
+      </c>
+      <c r="F4">
+        <v>30</v>
+      </c>
+      <c r="G4">
+        <v>211</v>
+      </c>
+      <c r="H4">
+        <v>259</v>
+      </c>
+      <c r="I4">
+        <v>1717</v>
+      </c>
+      <c r="J4">
+        <v>29</v>
+      </c>
+      <c r="K4">
+        <v>17</v>
+      </c>
+      <c r="L4">
         <v>208</v>
       </c>
-      <c r="F4">
+      <c r="M4">
         <v>1692</v>
       </c>
-      <c r="G4">
+      <c r="N4">
         <v>167</v>
       </c>
-      <c r="H4">
+      <c r="O4">
         <v>550</v>
       </c>
-      <c r="I4">
-        <v>669</v>
-      </c>
-      <c r="J4">
+      <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <v>59</v>
+      </c>
+      <c r="R4">
+        <v>198</v>
+      </c>
+      <c r="S4">
+        <v>226</v>
+      </c>
+      <c r="T4">
+        <v>46</v>
+      </c>
+      <c r="U4">
+        <v>140</v>
+      </c>
+      <c r="V4">
         <v>26</v>
       </c>
-      <c r="K4">
+      <c r="W4">
         <v>254</v>
       </c>
-      <c r="L4">
+      <c r="X4">
         <v>11</v>
       </c>
-      <c r="M4">
+      <c r="Y4">
         <v>3</v>
       </c>
-      <c r="N4">
+      <c r="Z4">
         <v>89</v>
       </c>
-      <c r="O4">
+      <c r="AA4">
         <v>1064</v>
       </c>
-      <c r="P4">
+      <c r="AB4">
         <v>5</v>
       </c>
-      <c r="Q4">
+      <c r="AC4">
         <v>27</v>
       </c>
-      <c r="R4">
+      <c r="AD4">
         <v>302</v>
       </c>
-      <c r="S4">
+      <c r="AE4">
         <v>310</v>
       </c>
-      <c r="T4">
+      <c r="AF4">
         <v>4</v>
       </c>
-      <c r="U4">
+      <c r="AG4">
         <v>20</v>
       </c>
-      <c r="V4">
+      <c r="AH4">
         <v>5</v>
       </c>
-      <c r="W4">
+      <c r="AI4">
         <v>243</v>
       </c>
-      <c r="X4">
-        <v>0</v>
-      </c>
-      <c r="Y4">
-        <v>0</v>
-      </c>
-      <c r="Z4">
+      <c r="AJ4">
+        <v>0</v>
+      </c>
+      <c r="AK4">
+        <v>0</v>
+      </c>
+      <c r="AL4">
         <v>3</v>
       </c>
-      <c r="AA4">
+      <c r="AM4">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:27">
+    <row r="5" spans="1:39">
       <c r="A5" s="1" t="s">
         <v>17</v>
       </c>
@@ -4903,79 +5089,115 @@
         <v>0</v>
       </c>
       <c r="D5">
-        <v>673</v>
+        <v>2</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>123</v>
       </c>
       <c r="F5">
+        <v>2</v>
+      </c>
+      <c r="G5">
+        <v>384</v>
+      </c>
+      <c r="H5">
+        <v>8</v>
+      </c>
+      <c r="I5">
+        <v>138</v>
+      </c>
+      <c r="J5">
+        <v>11</v>
+      </c>
+      <c r="K5">
+        <v>5</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
+      <c r="M5">
         <v>27</v>
       </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
         <v>11</v>
       </c>
-      <c r="I5">
-        <v>981</v>
-      </c>
-      <c r="J5">
+      <c r="P5">
+        <v>146</v>
+      </c>
+      <c r="Q5">
+        <v>10</v>
+      </c>
+      <c r="R5">
+        <v>138</v>
+      </c>
+      <c r="S5">
+        <v>457</v>
+      </c>
+      <c r="T5">
+        <v>3</v>
+      </c>
+      <c r="U5">
+        <v>227</v>
+      </c>
+      <c r="V5">
         <v>1090</v>
       </c>
-      <c r="K5">
+      <c r="W5">
         <v>11</v>
       </c>
-      <c r="L5">
+      <c r="X5">
         <v>6</v>
       </c>
-      <c r="M5">
+      <c r="Y5">
         <v>11</v>
       </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
-      <c r="O5">
-        <v>0</v>
-      </c>
-      <c r="P5">
+      <c r="Z5">
+        <v>0</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
         <v>4</v>
       </c>
-      <c r="Q5">
-        <v>0</v>
-      </c>
-      <c r="R5">
+      <c r="AC5">
+        <v>0</v>
+      </c>
+      <c r="AD5">
         <v>57</v>
       </c>
-      <c r="S5">
+      <c r="AE5">
         <v>4</v>
       </c>
-      <c r="T5">
+      <c r="AF5">
         <v>213</v>
       </c>
-      <c r="U5">
+      <c r="AG5">
         <v>10</v>
       </c>
-      <c r="V5">
-        <v>0</v>
-      </c>
-      <c r="W5">
+      <c r="AH5">
+        <v>0</v>
+      </c>
+      <c r="AI5">
         <v>6</v>
       </c>
-      <c r="X5">
-        <v>1</v>
-      </c>
-      <c r="Y5">
+      <c r="AJ5">
+        <v>1</v>
+      </c>
+      <c r="AK5">
         <v>42</v>
       </c>
-      <c r="Z5">
+      <c r="AL5">
         <v>1521</v>
       </c>
-      <c r="AA5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:27">
+      <c r="AM5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:39">
       <c r="A6" s="1" t="s">
         <v>18</v>
       </c>
@@ -4986,79 +5208,115 @@
         <v>38</v>
       </c>
       <c r="D6">
-        <v>998</v>
+        <v>221</v>
       </c>
       <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>53</v>
+      </c>
+      <c r="G6">
+        <v>32</v>
+      </c>
+      <c r="H6">
+        <v>33</v>
+      </c>
+      <c r="I6">
+        <v>32</v>
+      </c>
+      <c r="J6">
+        <v>53</v>
+      </c>
+      <c r="K6">
+        <v>573</v>
+      </c>
+      <c r="L6">
         <v>18</v>
       </c>
-      <c r="F6">
+      <c r="M6">
         <v>75</v>
       </c>
-      <c r="G6">
+      <c r="N6">
         <v>21</v>
       </c>
-      <c r="H6">
+      <c r="O6">
         <v>71</v>
       </c>
-      <c r="I6">
-        <v>406</v>
-      </c>
-      <c r="J6">
+      <c r="P6">
+        <v>22</v>
+      </c>
+      <c r="Q6">
+        <v>34</v>
+      </c>
+      <c r="R6">
+        <v>142</v>
+      </c>
+      <c r="S6">
+        <v>82</v>
+      </c>
+      <c r="T6">
+        <v>64</v>
+      </c>
+      <c r="U6">
+        <v>62</v>
+      </c>
+      <c r="V6">
         <v>153</v>
       </c>
-      <c r="K6">
+      <c r="W6">
         <v>15</v>
       </c>
-      <c r="L6">
+      <c r="X6">
         <v>41</v>
       </c>
-      <c r="M6">
+      <c r="Y6">
         <v>8</v>
       </c>
-      <c r="N6">
+      <c r="Z6">
         <v>15</v>
       </c>
-      <c r="O6">
+      <c r="AA6">
         <v>11</v>
       </c>
-      <c r="P6">
+      <c r="AB6">
         <v>35</v>
       </c>
-      <c r="Q6">
+      <c r="AC6">
         <v>5</v>
       </c>
-      <c r="R6">
+      <c r="AD6">
         <v>120</v>
       </c>
-      <c r="S6">
+      <c r="AE6">
         <v>43</v>
       </c>
-      <c r="T6">
+      <c r="AF6">
         <v>278</v>
       </c>
-      <c r="U6">
-        <v>1</v>
-      </c>
-      <c r="V6">
+      <c r="AG6">
+        <v>1</v>
+      </c>
+      <c r="AH6">
         <v>575</v>
       </c>
-      <c r="W6">
+      <c r="AI6">
         <v>584</v>
       </c>
-      <c r="X6">
+      <c r="AJ6">
         <v>8</v>
       </c>
-      <c r="Y6">
+      <c r="AK6">
         <v>388</v>
       </c>
-      <c r="Z6">
+      <c r="AL6">
         <v>1828</v>
       </c>
-      <c r="AA6">
+      <c r="AM6">
         <v>48</v>
       </c>
     </row>
-    <row r="7" spans="1:27">
+    <row r="7" spans="1:39">
       <c r="A7" s="1" t="s">
         <v>19</v>
       </c>
@@ -5069,79 +5327,115 @@
         <v>105</v>
       </c>
       <c r="D7">
-        <v>1138</v>
+        <v>29</v>
       </c>
       <c r="E7">
+        <v>48</v>
+      </c>
+      <c r="F7">
+        <v>74</v>
+      </c>
+      <c r="G7">
+        <v>341</v>
+      </c>
+      <c r="H7">
+        <v>15</v>
+      </c>
+      <c r="I7">
+        <v>346</v>
+      </c>
+      <c r="J7">
+        <v>235</v>
+      </c>
+      <c r="K7">
+        <v>50</v>
+      </c>
+      <c r="L7">
         <v>28</v>
       </c>
-      <c r="F7">
+      <c r="M7">
         <v>388</v>
       </c>
-      <c r="G7">
+      <c r="N7">
         <v>52</v>
       </c>
-      <c r="H7">
+      <c r="O7">
         <v>116</v>
       </c>
-      <c r="I7">
-        <v>855</v>
-      </c>
-      <c r="J7">
+      <c r="P7">
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <v>13</v>
+      </c>
+      <c r="R7">
+        <v>246</v>
+      </c>
+      <c r="S7">
+        <v>329</v>
+      </c>
+      <c r="T7">
+        <v>41</v>
+      </c>
+      <c r="U7">
+        <v>226</v>
+      </c>
+      <c r="V7">
         <v>112</v>
       </c>
-      <c r="K7">
+      <c r="W7">
         <v>30</v>
       </c>
-      <c r="L7">
+      <c r="X7">
         <v>12</v>
       </c>
-      <c r="M7">
+      <c r="Y7">
         <v>116</v>
       </c>
-      <c r="N7">
+      <c r="Z7">
         <v>17</v>
       </c>
-      <c r="O7">
+      <c r="AA7">
         <v>2</v>
       </c>
-      <c r="P7">
+      <c r="AB7">
         <v>104</v>
       </c>
-      <c r="Q7">
+      <c r="AC7">
         <v>11</v>
       </c>
-      <c r="R7">
+      <c r="AD7">
         <v>273</v>
       </c>
-      <c r="S7">
+      <c r="AE7">
         <v>64</v>
       </c>
-      <c r="T7">
+      <c r="AF7">
         <v>146</v>
       </c>
-      <c r="U7">
+      <c r="AG7">
         <v>13</v>
       </c>
-      <c r="V7">
-        <v>0</v>
-      </c>
-      <c r="W7">
-        <v>0</v>
-      </c>
-      <c r="X7">
-        <v>1</v>
-      </c>
-      <c r="Y7">
-        <v>0</v>
-      </c>
-      <c r="Z7">
-        <v>0</v>
-      </c>
-      <c r="AA7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:27">
+      <c r="AH7">
+        <v>0</v>
+      </c>
+      <c r="AI7">
+        <v>0</v>
+      </c>
+      <c r="AJ7">
+        <v>1</v>
+      </c>
+      <c r="AK7">
+        <v>0</v>
+      </c>
+      <c r="AL7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:39">
       <c r="A8" s="1" t="s">
         <v>20</v>
       </c>
@@ -5152,79 +5446,115 @@
         <v>56</v>
       </c>
       <c r="D8">
-        <v>1498</v>
+        <v>857</v>
       </c>
       <c r="E8">
+        <v>5</v>
+      </c>
+      <c r="F8">
+        <v>83</v>
+      </c>
+      <c r="G8">
+        <v>9</v>
+      </c>
+      <c r="H8">
+        <v>218</v>
+      </c>
+      <c r="I8">
+        <v>2</v>
+      </c>
+      <c r="J8">
+        <v>246</v>
+      </c>
+      <c r="K8">
+        <v>78</v>
+      </c>
+      <c r="L8">
         <v>62</v>
       </c>
-      <c r="F8">
+      <c r="M8">
         <v>136</v>
       </c>
-      <c r="G8">
+      <c r="N8">
         <v>47</v>
       </c>
-      <c r="H8">
+      <c r="O8">
         <v>101</v>
       </c>
-      <c r="I8">
-        <v>234</v>
-      </c>
-      <c r="J8">
+      <c r="P8">
+        <v>0</v>
+      </c>
+      <c r="Q8">
+        <v>109</v>
+      </c>
+      <c r="R8">
+        <v>47</v>
+      </c>
+      <c r="S8">
+        <v>11</v>
+      </c>
+      <c r="T8">
+        <v>54</v>
+      </c>
+      <c r="U8">
+        <v>13</v>
+      </c>
+      <c r="V8">
         <v>216</v>
       </c>
-      <c r="K8">
+      <c r="W8">
         <v>80</v>
       </c>
-      <c r="L8">
+      <c r="X8">
         <v>172</v>
       </c>
-      <c r="M8">
+      <c r="Y8">
         <v>89</v>
       </c>
-      <c r="N8">
+      <c r="Z8">
         <v>61</v>
       </c>
-      <c r="O8">
+      <c r="AA8">
         <v>178</v>
       </c>
-      <c r="P8">
+      <c r="AB8">
         <v>17</v>
       </c>
-      <c r="Q8">
+      <c r="AC8">
         <v>41</v>
       </c>
-      <c r="R8">
+      <c r="AD8">
         <v>170</v>
       </c>
-      <c r="S8">
+      <c r="AE8">
         <v>151</v>
       </c>
-      <c r="T8">
+      <c r="AF8">
         <v>57</v>
       </c>
-      <c r="U8">
+      <c r="AG8">
         <v>4</v>
       </c>
-      <c r="V8">
+      <c r="AH8">
         <v>1029</v>
       </c>
-      <c r="W8">
+      <c r="AI8">
         <v>76</v>
       </c>
-      <c r="X8">
+      <c r="AJ8">
         <v>3</v>
       </c>
-      <c r="Y8">
+      <c r="AK8">
         <v>164</v>
       </c>
-      <c r="Z8">
+      <c r="AL8">
         <v>34</v>
       </c>
-      <c r="AA8">
+      <c r="AM8">
         <v>2994</v>
       </c>
     </row>
-    <row r="9" spans="1:27">
+    <row r="9" spans="1:39">
       <c r="A9" s="1" t="s">
         <v>21</v>
       </c>
@@ -5235,79 +5565,115 @@
         <v>80</v>
       </c>
       <c r="D9">
-        <v>2883</v>
+        <v>17</v>
       </c>
       <c r="E9">
+        <v>51</v>
+      </c>
+      <c r="F9">
+        <v>22</v>
+      </c>
+      <c r="G9">
+        <v>908</v>
+      </c>
+      <c r="H9">
+        <v>34</v>
+      </c>
+      <c r="I9">
+        <v>1653</v>
+      </c>
+      <c r="J9">
+        <v>160</v>
+      </c>
+      <c r="K9">
+        <v>38</v>
+      </c>
+      <c r="L9">
         <v>23</v>
       </c>
-      <c r="F9">
+      <c r="M9">
         <v>218</v>
       </c>
-      <c r="G9">
+      <c r="N9">
         <v>22</v>
       </c>
-      <c r="H9">
+      <c r="O9">
         <v>212</v>
       </c>
-      <c r="I9">
-        <v>2355</v>
-      </c>
-      <c r="J9">
+      <c r="P9">
+        <v>79</v>
+      </c>
+      <c r="Q9">
+        <v>32</v>
+      </c>
+      <c r="R9">
+        <v>418</v>
+      </c>
+      <c r="S9">
+        <v>1392</v>
+      </c>
+      <c r="T9">
+        <v>26</v>
+      </c>
+      <c r="U9">
+        <v>408</v>
+      </c>
+      <c r="V9">
         <v>221</v>
       </c>
-      <c r="K9">
+      <c r="W9">
         <v>50</v>
       </c>
-      <c r="L9">
+      <c r="X9">
         <v>30</v>
       </c>
-      <c r="M9">
+      <c r="Y9">
         <v>174</v>
       </c>
-      <c r="N9">
+      <c r="Z9">
         <v>23</v>
       </c>
-      <c r="O9">
-        <v>1</v>
-      </c>
-      <c r="P9">
+      <c r="AA9">
+        <v>1</v>
+      </c>
+      <c r="AB9">
         <v>44</v>
       </c>
-      <c r="Q9">
+      <c r="AC9">
         <v>4</v>
       </c>
-      <c r="R9">
+      <c r="AD9">
         <v>379</v>
       </c>
-      <c r="S9">
+      <c r="AE9">
         <v>91</v>
       </c>
-      <c r="T9">
+      <c r="AF9">
         <v>122</v>
       </c>
-      <c r="U9">
+      <c r="AG9">
         <v>93</v>
       </c>
-      <c r="V9">
+      <c r="AH9">
         <v>8</v>
       </c>
-      <c r="W9">
+      <c r="AI9">
         <v>12</v>
       </c>
-      <c r="X9">
-        <v>0</v>
-      </c>
-      <c r="Y9">
+      <c r="AJ9">
+        <v>0</v>
+      </c>
+      <c r="AK9">
         <v>27</v>
       </c>
-      <c r="Z9">
+      <c r="AL9">
         <v>419</v>
       </c>
-      <c r="AA9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:27">
+      <c r="AM9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:39">
       <c r="A10" s="1" t="s">
         <v>22</v>
       </c>
@@ -5318,79 +5684,115 @@
         <v>568</v>
       </c>
       <c r="D10">
-        <v>1386</v>
+        <v>777</v>
       </c>
       <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10">
+        <v>125</v>
+      </c>
+      <c r="G10">
+        <v>11</v>
+      </c>
+      <c r="H10">
+        <v>311</v>
+      </c>
+      <c r="I10">
+        <v>14</v>
+      </c>
+      <c r="J10">
+        <v>101</v>
+      </c>
+      <c r="K10">
+        <v>46</v>
+      </c>
+      <c r="L10">
         <v>289</v>
       </c>
-      <c r="F10">
+      <c r="M10">
         <v>1190</v>
       </c>
-      <c r="G10">
+      <c r="N10">
         <v>540</v>
       </c>
-      <c r="H10">
+      <c r="O10">
         <v>1109</v>
       </c>
-      <c r="I10">
-        <v>321</v>
-      </c>
-      <c r="J10">
-        <v>1</v>
-      </c>
-      <c r="K10">
+      <c r="P10">
+        <v>1</v>
+      </c>
+      <c r="Q10">
+        <v>106</v>
+      </c>
+      <c r="R10">
+        <v>84</v>
+      </c>
+      <c r="S10">
+        <v>49</v>
+      </c>
+      <c r="T10">
+        <v>50</v>
+      </c>
+      <c r="U10">
+        <v>31</v>
+      </c>
+      <c r="V10">
+        <v>1</v>
+      </c>
+      <c r="W10">
         <v>1351</v>
       </c>
-      <c r="L10">
+      <c r="X10">
         <v>200</v>
       </c>
-      <c r="M10">
+      <c r="Y10">
         <v>40</v>
       </c>
-      <c r="N10">
+      <c r="Z10">
         <v>417</v>
       </c>
-      <c r="O10">
+      <c r="AA10">
         <v>1316</v>
       </c>
-      <c r="P10">
+      <c r="AB10">
         <v>209</v>
       </c>
-      <c r="Q10">
+      <c r="AC10">
         <v>1529</v>
       </c>
-      <c r="R10">
+      <c r="AD10">
         <v>144</v>
       </c>
-      <c r="S10">
+      <c r="AE10">
         <v>631</v>
       </c>
-      <c r="T10">
+      <c r="AF10">
         <v>27</v>
       </c>
-      <c r="U10">
+      <c r="AG10">
         <v>20</v>
       </c>
-      <c r="V10">
-        <v>0</v>
-      </c>
-      <c r="W10">
-        <v>0</v>
-      </c>
-      <c r="X10">
-        <v>0</v>
-      </c>
-      <c r="Y10">
-        <v>0</v>
-      </c>
-      <c r="Z10">
-        <v>0</v>
-      </c>
-      <c r="AA10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:27">
+      <c r="AH10">
+        <v>0</v>
+      </c>
+      <c r="AI10">
+        <v>0</v>
+      </c>
+      <c r="AJ10">
+        <v>0</v>
+      </c>
+      <c r="AK10">
+        <v>0</v>
+      </c>
+      <c r="AL10">
+        <v>0</v>
+      </c>
+      <c r="AM10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:39">
       <c r="A11" s="1" t="s">
         <v>23</v>
       </c>
@@ -5401,79 +5803,115 @@
         <v>67</v>
       </c>
       <c r="D11">
-        <v>1395</v>
+        <v>12</v>
       </c>
       <c r="E11">
+        <v>548</v>
+      </c>
+      <c r="F11">
+        <v>34</v>
+      </c>
+      <c r="G11">
+        <v>552</v>
+      </c>
+      <c r="H11">
+        <v>25</v>
+      </c>
+      <c r="I11">
+        <v>193</v>
+      </c>
+      <c r="J11">
+        <v>22</v>
+      </c>
+      <c r="K11">
+        <v>9</v>
+      </c>
+      <c r="L11">
         <v>28</v>
       </c>
-      <c r="F11">
+      <c r="M11">
         <v>242</v>
       </c>
-      <c r="G11">
+      <c r="N11">
         <v>37</v>
       </c>
-      <c r="H11">
+      <c r="O11">
         <v>200</v>
       </c>
-      <c r="I11">
-        <v>1732</v>
-      </c>
-      <c r="J11">
+      <c r="P11">
+        <v>18</v>
+      </c>
+      <c r="Q11">
+        <v>43</v>
+      </c>
+      <c r="R11">
+        <v>473</v>
+      </c>
+      <c r="S11">
+        <v>855</v>
+      </c>
+      <c r="T11">
+        <v>11</v>
+      </c>
+      <c r="U11">
+        <v>332</v>
+      </c>
+      <c r="V11">
         <v>415</v>
       </c>
-      <c r="K11">
+      <c r="W11">
         <v>28</v>
       </c>
-      <c r="L11">
+      <c r="X11">
         <v>56</v>
       </c>
-      <c r="M11">
+      <c r="Y11">
         <v>52</v>
       </c>
-      <c r="N11">
+      <c r="Z11">
         <v>14</v>
       </c>
-      <c r="O11">
+      <c r="AA11">
         <v>23</v>
       </c>
-      <c r="P11">
+      <c r="AB11">
         <v>22</v>
       </c>
-      <c r="Q11">
+      <c r="AC11">
         <v>13</v>
       </c>
-      <c r="R11">
+      <c r="AD11">
         <v>660</v>
       </c>
-      <c r="S11">
+      <c r="AE11">
         <v>56</v>
       </c>
-      <c r="T11">
+      <c r="AF11">
         <v>790</v>
       </c>
-      <c r="U11">
+      <c r="AG11">
         <v>148</v>
       </c>
-      <c r="V11">
+      <c r="AH11">
         <v>2</v>
       </c>
-      <c r="W11">
+      <c r="AI11">
         <v>68</v>
       </c>
-      <c r="X11">
+      <c r="AJ11">
         <v>35</v>
       </c>
-      <c r="Y11">
+      <c r="AK11">
         <v>713</v>
       </c>
-      <c r="Z11">
+      <c r="AL11">
         <v>82</v>
       </c>
-      <c r="AA11">
+      <c r="AM11">
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:27">
+    <row r="12" spans="1:39">
       <c r="A12" s="1" t="s">
         <v>24</v>
       </c>
@@ -5484,79 +5922,115 @@
         <v>155</v>
       </c>
       <c r="D12">
-        <v>283</v>
+        <v>30</v>
       </c>
       <c r="E12">
+        <v>35</v>
+      </c>
+      <c r="F12">
+        <v>168</v>
+      </c>
+      <c r="G12">
+        <v>2</v>
+      </c>
+      <c r="H12">
+        <v>6</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>10</v>
+      </c>
+      <c r="K12">
+        <v>32</v>
+      </c>
+      <c r="L12">
         <v>55</v>
       </c>
-      <c r="F12">
+      <c r="M12">
         <v>134</v>
       </c>
-      <c r="G12">
+      <c r="N12">
         <v>63</v>
       </c>
-      <c r="H12">
+      <c r="O12">
         <v>203</v>
       </c>
-      <c r="I12">
-        <v>616</v>
-      </c>
-      <c r="J12">
+      <c r="P12">
+        <v>48</v>
+      </c>
+      <c r="Q12">
+        <v>18</v>
+      </c>
+      <c r="R12">
+        <v>246</v>
+      </c>
+      <c r="S12">
+        <v>147</v>
+      </c>
+      <c r="T12">
+        <v>102</v>
+      </c>
+      <c r="U12">
+        <v>55</v>
+      </c>
+      <c r="V12">
         <v>427</v>
       </c>
-      <c r="K12">
+      <c r="W12">
         <v>19</v>
       </c>
-      <c r="L12">
+      <c r="X12">
         <v>69</v>
       </c>
-      <c r="M12">
+      <c r="Y12">
         <v>45</v>
       </c>
-      <c r="N12">
+      <c r="Z12">
         <v>82</v>
       </c>
-      <c r="O12">
+      <c r="AA12">
         <v>41</v>
       </c>
-      <c r="P12">
+      <c r="AB12">
         <v>94</v>
       </c>
-      <c r="Q12">
+      <c r="AC12">
         <v>26</v>
       </c>
-      <c r="R12">
+      <c r="AD12">
         <v>137</v>
       </c>
-      <c r="S12">
+      <c r="AE12">
         <v>20</v>
       </c>
-      <c r="T12">
+      <c r="AF12">
         <v>209</v>
       </c>
-      <c r="U12">
+      <c r="AG12">
         <v>29</v>
       </c>
-      <c r="V12">
+      <c r="AH12">
         <v>2</v>
       </c>
-      <c r="W12">
+      <c r="AI12">
         <v>5</v>
       </c>
-      <c r="X12">
+      <c r="AJ12">
         <v>380</v>
       </c>
-      <c r="Y12">
-        <v>0</v>
-      </c>
-      <c r="Z12">
-        <v>0</v>
-      </c>
-      <c r="AA12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:27">
+      <c r="AK12">
+        <v>0</v>
+      </c>
+      <c r="AL12">
+        <v>0</v>
+      </c>
+      <c r="AM12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:39">
       <c r="A13" s="1" t="s">
         <v>25</v>
       </c>
@@ -5567,79 +6041,115 @@
         <v>72</v>
       </c>
       <c r="D13">
-        <v>387</v>
+        <v>7</v>
       </c>
       <c r="E13">
+        <v>98</v>
+      </c>
+      <c r="F13">
+        <v>65</v>
+      </c>
+      <c r="G13">
+        <v>9</v>
+      </c>
+      <c r="H13">
+        <v>2</v>
+      </c>
+      <c r="I13">
+        <v>2</v>
+      </c>
+      <c r="J13">
+        <v>74</v>
+      </c>
+      <c r="K13">
+        <v>130</v>
+      </c>
+      <c r="L13">
         <v>11</v>
       </c>
-      <c r="F13">
+      <c r="M13">
         <v>69</v>
       </c>
-      <c r="G13">
+      <c r="N13">
         <v>77</v>
       </c>
-      <c r="H13">
+      <c r="O13">
         <v>19</v>
       </c>
-      <c r="I13">
-        <v>771</v>
-      </c>
-      <c r="J13">
+      <c r="P13">
+        <v>6</v>
+      </c>
+      <c r="Q13">
+        <v>7</v>
+      </c>
+      <c r="R13">
+        <v>286</v>
+      </c>
+      <c r="S13">
+        <v>292</v>
+      </c>
+      <c r="T13">
+        <v>118</v>
+      </c>
+      <c r="U13">
+        <v>62</v>
+      </c>
+      <c r="V13">
         <v>330</v>
       </c>
-      <c r="K13">
+      <c r="W13">
         <v>6</v>
       </c>
-      <c r="L13">
+      <c r="X13">
         <v>22</v>
       </c>
-      <c r="M13">
+      <c r="Y13">
         <v>9</v>
       </c>
-      <c r="N13">
+      <c r="Z13">
         <v>3</v>
       </c>
-      <c r="O13">
-        <v>0</v>
-      </c>
-      <c r="P13">
+      <c r="AA13">
+        <v>0</v>
+      </c>
+      <c r="AB13">
         <v>3</v>
       </c>
-      <c r="Q13">
+      <c r="AC13">
         <v>4</v>
       </c>
-      <c r="R13">
+      <c r="AD13">
         <v>258</v>
       </c>
-      <c r="S13">
+      <c r="AE13">
         <v>8</v>
       </c>
-      <c r="T13">
+      <c r="AF13">
         <v>1241</v>
       </c>
-      <c r="U13">
+      <c r="AG13">
         <v>18</v>
       </c>
-      <c r="V13">
-        <v>0</v>
-      </c>
-      <c r="W13">
-        <v>0</v>
-      </c>
-      <c r="X13">
+      <c r="AH13">
+        <v>0</v>
+      </c>
+      <c r="AI13">
+        <v>0</v>
+      </c>
+      <c r="AJ13">
         <v>12</v>
       </c>
-      <c r="Y13">
+      <c r="AK13">
         <v>3</v>
       </c>
-      <c r="Z13">
-        <v>1</v>
-      </c>
-      <c r="AA13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:27">
+      <c r="AL13">
+        <v>1</v>
+      </c>
+      <c r="AM13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:39">
       <c r="A14" s="1" t="s">
         <v>26</v>
       </c>
@@ -5650,79 +6160,115 @@
         <v>1</v>
       </c>
       <c r="D14">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="E14">
+        <v>60</v>
+      </c>
+      <c r="F14">
+        <v>3</v>
+      </c>
+      <c r="G14">
+        <v>10</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>4</v>
+      </c>
+      <c r="J14">
+        <v>1</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
         <v>2</v>
       </c>
-      <c r="F14">
+      <c r="M14">
         <v>21</v>
       </c>
-      <c r="G14">
+      <c r="N14">
         <v>21</v>
       </c>
-      <c r="H14">
+      <c r="O14">
         <v>6</v>
       </c>
-      <c r="I14">
-        <v>858</v>
-      </c>
-      <c r="J14">
+      <c r="P14">
+        <v>9</v>
+      </c>
+      <c r="Q14">
+        <v>3</v>
+      </c>
+      <c r="R14">
+        <v>438</v>
+      </c>
+      <c r="S14">
+        <v>270</v>
+      </c>
+      <c r="T14">
+        <v>84</v>
+      </c>
+      <c r="U14">
+        <v>54</v>
+      </c>
+      <c r="V14">
         <v>881</v>
       </c>
-      <c r="K14">
-        <v>1</v>
-      </c>
-      <c r="L14">
+      <c r="W14">
+        <v>1</v>
+      </c>
+      <c r="X14">
         <v>14</v>
       </c>
-      <c r="M14">
-        <v>0</v>
-      </c>
-      <c r="N14">
-        <v>0</v>
-      </c>
-      <c r="O14">
-        <v>0</v>
-      </c>
-      <c r="P14">
+      <c r="Y14">
+        <v>0</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+      <c r="AA14">
+        <v>0</v>
+      </c>
+      <c r="AB14">
         <v>7</v>
       </c>
-      <c r="Q14">
-        <v>0</v>
-      </c>
-      <c r="R14">
+      <c r="AC14">
+        <v>0</v>
+      </c>
+      <c r="AD14">
         <v>95</v>
       </c>
-      <c r="S14">
-        <v>1</v>
-      </c>
-      <c r="T14">
+      <c r="AE14">
+        <v>1</v>
+      </c>
+      <c r="AF14">
         <v>1492</v>
       </c>
-      <c r="U14">
+      <c r="AG14">
         <v>11</v>
       </c>
-      <c r="V14">
-        <v>0</v>
-      </c>
-      <c r="W14">
-        <v>0</v>
-      </c>
-      <c r="X14">
+      <c r="AH14">
+        <v>0</v>
+      </c>
+      <c r="AI14">
+        <v>0</v>
+      </c>
+      <c r="AJ14">
         <v>6</v>
       </c>
-      <c r="Y14">
+      <c r="AK14">
         <v>5</v>
       </c>
-      <c r="Z14">
-        <v>0</v>
-      </c>
-      <c r="AA14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:27">
+      <c r="AL14">
+        <v>0</v>
+      </c>
+      <c r="AM14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:39">
       <c r="A15" s="1" t="s">
         <v>27</v>
       </c>
@@ -5733,79 +6279,115 @@
         <v>3</v>
       </c>
       <c r="D15">
-        <v>719</v>
+        <v>32</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>70</v>
       </c>
       <c r="F15">
+        <v>35</v>
+      </c>
+      <c r="G15">
+        <v>205</v>
+      </c>
+      <c r="H15">
+        <v>8</v>
+      </c>
+      <c r="I15">
+        <v>90</v>
+      </c>
+      <c r="J15">
+        <v>78</v>
+      </c>
+      <c r="K15">
+        <v>201</v>
+      </c>
+      <c r="L15">
+        <v>1</v>
+      </c>
+      <c r="M15">
         <v>6</v>
       </c>
-      <c r="G15">
-        <v>1</v>
-      </c>
-      <c r="H15">
+      <c r="N15">
+        <v>1</v>
+      </c>
+      <c r="O15">
         <v>10</v>
       </c>
-      <c r="I15">
-        <v>1220</v>
-      </c>
-      <c r="J15">
+      <c r="P15">
+        <v>61</v>
+      </c>
+      <c r="Q15">
+        <v>98</v>
+      </c>
+      <c r="R15">
+        <v>273</v>
+      </c>
+      <c r="S15">
+        <v>535</v>
+      </c>
+      <c r="T15">
+        <v>122</v>
+      </c>
+      <c r="U15">
+        <v>131</v>
+      </c>
+      <c r="V15">
         <v>166</v>
       </c>
-      <c r="K15">
+      <c r="W15">
         <v>10</v>
       </c>
-      <c r="L15">
+      <c r="X15">
         <v>16</v>
       </c>
-      <c r="M15">
+      <c r="Y15">
         <v>2</v>
       </c>
-      <c r="N15">
-        <v>1</v>
-      </c>
-      <c r="O15">
+      <c r="Z15">
+        <v>1</v>
+      </c>
+      <c r="AA15">
         <v>23</v>
       </c>
-      <c r="P15">
+      <c r="AB15">
         <v>6</v>
       </c>
-      <c r="Q15">
+      <c r="AC15">
         <v>5</v>
       </c>
-      <c r="R15">
+      <c r="AD15">
         <v>215</v>
       </c>
-      <c r="S15">
+      <c r="AE15">
         <v>6</v>
       </c>
-      <c r="T15">
+      <c r="AF15">
         <v>49</v>
       </c>
-      <c r="U15">
+      <c r="AG15">
         <v>6</v>
       </c>
-      <c r="V15">
+      <c r="AH15">
         <v>269</v>
       </c>
-      <c r="W15">
+      <c r="AI15">
         <v>56</v>
       </c>
-      <c r="X15">
-        <v>0</v>
-      </c>
-      <c r="Y15">
+      <c r="AJ15">
+        <v>0</v>
+      </c>
+      <c r="AK15">
         <v>3685</v>
       </c>
-      <c r="Z15">
+      <c r="AL15">
         <v>327</v>
       </c>
-      <c r="AA15">
+      <c r="AM15">
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:27">
+    <row r="16" spans="1:39">
       <c r="A16" s="1" t="s">
         <v>28</v>
       </c>
@@ -5816,79 +6398,115 @@
         <v>0</v>
       </c>
       <c r="D16">
-        <v>176</v>
+        <v>13</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F16">
+        <v>6</v>
+      </c>
+      <c r="G16">
+        <v>42</v>
+      </c>
+      <c r="H16">
+        <v>5</v>
+      </c>
+      <c r="I16">
+        <v>12</v>
+      </c>
+      <c r="J16">
+        <v>43</v>
+      </c>
+      <c r="K16">
+        <v>51</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
         <v>3</v>
       </c>
-      <c r="G16">
-        <v>0</v>
-      </c>
-      <c r="H16">
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16">
         <v>2</v>
       </c>
-      <c r="I16">
-        <v>228</v>
-      </c>
-      <c r="J16">
+      <c r="P16">
+        <v>11</v>
+      </c>
+      <c r="Q16">
+        <v>17</v>
+      </c>
+      <c r="R16">
+        <v>34</v>
+      </c>
+      <c r="S16">
+        <v>97</v>
+      </c>
+      <c r="T16">
+        <v>17</v>
+      </c>
+      <c r="U16">
+        <v>52</v>
+      </c>
+      <c r="V16">
         <v>27</v>
       </c>
-      <c r="K16">
+      <c r="W16">
         <v>7</v>
       </c>
-      <c r="L16">
+      <c r="X16">
         <v>12</v>
       </c>
-      <c r="M16">
-        <v>0</v>
-      </c>
-      <c r="N16">
-        <v>1</v>
-      </c>
-      <c r="O16">
+      <c r="Y16">
+        <v>0</v>
+      </c>
+      <c r="Z16">
+        <v>1</v>
+      </c>
+      <c r="AA16">
         <v>9</v>
       </c>
-      <c r="P16">
-        <v>0</v>
-      </c>
-      <c r="Q16">
-        <v>1</v>
-      </c>
-      <c r="R16">
+      <c r="AB16">
+        <v>0</v>
+      </c>
+      <c r="AC16">
+        <v>1</v>
+      </c>
+      <c r="AD16">
         <v>48</v>
       </c>
-      <c r="S16">
-        <v>1</v>
-      </c>
-      <c r="T16">
+      <c r="AE16">
+        <v>1</v>
+      </c>
+      <c r="AF16">
         <v>19</v>
       </c>
-      <c r="U16">
+      <c r="AG16">
         <v>9</v>
       </c>
-      <c r="V16">
+      <c r="AH16">
         <v>111</v>
       </c>
-      <c r="W16">
+      <c r="AI16">
         <v>9</v>
       </c>
-      <c r="X16">
-        <v>1</v>
-      </c>
-      <c r="Y16">
+      <c r="AJ16">
+        <v>1</v>
+      </c>
+      <c r="AK16">
         <v>722</v>
       </c>
-      <c r="Z16">
+      <c r="AL16">
         <v>19</v>
       </c>
-      <c r="AA16">
+      <c r="AM16">
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:27">
+    <row r="17" spans="1:39">
       <c r="A17" s="1" t="s">
         <v>29</v>
       </c>
@@ -5899,79 +6517,115 @@
         <v>12</v>
       </c>
       <c r="D17">
-        <v>1505</v>
+        <v>7</v>
       </c>
       <c r="E17">
+        <v>115</v>
+      </c>
+      <c r="F17">
+        <v>22</v>
+      </c>
+      <c r="G17">
+        <v>780</v>
+      </c>
+      <c r="H17">
+        <v>53</v>
+      </c>
+      <c r="I17">
+        <v>381</v>
+      </c>
+      <c r="J17">
+        <v>64</v>
+      </c>
+      <c r="K17">
+        <v>83</v>
+      </c>
+      <c r="L17">
         <v>14</v>
       </c>
-      <c r="F17">
+      <c r="M17">
         <v>110</v>
       </c>
-      <c r="G17">
+      <c r="N17">
         <v>103</v>
       </c>
-      <c r="H17">
+      <c r="O17">
         <v>101</v>
       </c>
-      <c r="I17">
-        <v>2753</v>
-      </c>
-      <c r="J17">
+      <c r="P17">
+        <v>387</v>
+      </c>
+      <c r="Q17">
+        <v>47</v>
+      </c>
+      <c r="R17">
+        <v>204</v>
+      </c>
+      <c r="S17">
+        <v>1584</v>
+      </c>
+      <c r="T17">
+        <v>44</v>
+      </c>
+      <c r="U17">
+        <v>487</v>
+      </c>
+      <c r="V17">
         <v>136</v>
       </c>
-      <c r="K17">
+      <c r="W17">
         <v>26</v>
       </c>
-      <c r="L17">
+      <c r="X17">
         <v>45</v>
       </c>
-      <c r="M17">
+      <c r="Y17">
         <v>93</v>
       </c>
-      <c r="N17">
+      <c r="Z17">
         <v>12</v>
       </c>
-      <c r="O17">
+      <c r="AA17">
         <v>24</v>
       </c>
-      <c r="P17">
+      <c r="AB17">
         <v>9</v>
       </c>
-      <c r="Q17">
+      <c r="AC17">
         <v>35</v>
       </c>
-      <c r="R17">
+      <c r="AD17">
         <v>336</v>
       </c>
-      <c r="S17">
+      <c r="AE17">
         <v>35</v>
       </c>
-      <c r="T17">
+      <c r="AF17">
         <v>199</v>
       </c>
-      <c r="U17">
+      <c r="AG17">
         <v>73</v>
       </c>
-      <c r="V17">
+      <c r="AH17">
         <v>15</v>
       </c>
-      <c r="W17">
+      <c r="AI17">
         <v>11</v>
       </c>
-      <c r="X17">
-        <v>1</v>
-      </c>
-      <c r="Y17">
+      <c r="AJ17">
+        <v>1</v>
+      </c>
+      <c r="AK17">
         <v>438</v>
       </c>
-      <c r="Z17">
+      <c r="AL17">
         <v>21</v>
       </c>
-      <c r="AA17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:27">
+      <c r="AM17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:39">
       <c r="A18" s="1" t="s">
         <v>30</v>
       </c>
@@ -5982,79 +6636,115 @@
         <v>265</v>
       </c>
       <c r="D18">
-        <v>604</v>
+        <v>232</v>
       </c>
       <c r="E18">
+        <v>4</v>
+      </c>
+      <c r="F18">
+        <v>7</v>
+      </c>
+      <c r="G18">
+        <v>14</v>
+      </c>
+      <c r="H18">
+        <v>48</v>
+      </c>
+      <c r="I18">
+        <v>14</v>
+      </c>
+      <c r="J18">
+        <v>199</v>
+      </c>
+      <c r="K18">
+        <v>86</v>
+      </c>
+      <c r="L18">
         <v>131</v>
       </c>
-      <c r="F18">
+      <c r="M18">
         <v>758</v>
       </c>
-      <c r="G18">
+      <c r="N18">
         <v>71</v>
       </c>
-      <c r="H18">
+      <c r="O18">
         <v>376</v>
       </c>
-      <c r="I18">
-        <v>1922</v>
-      </c>
-      <c r="J18">
+      <c r="P18">
+        <v>4</v>
+      </c>
+      <c r="Q18">
+        <v>908</v>
+      </c>
+      <c r="R18">
+        <v>310</v>
+      </c>
+      <c r="S18">
+        <v>355</v>
+      </c>
+      <c r="T18">
+        <v>223</v>
+      </c>
+      <c r="U18">
+        <v>122</v>
+      </c>
+      <c r="V18">
         <v>14</v>
       </c>
-      <c r="K18">
+      <c r="W18">
         <v>75</v>
       </c>
-      <c r="L18">
+      <c r="X18">
         <v>74</v>
       </c>
-      <c r="M18">
+      <c r="Y18">
         <v>818</v>
       </c>
-      <c r="N18">
+      <c r="Z18">
         <v>254</v>
       </c>
-      <c r="O18">
+      <c r="AA18">
         <v>156</v>
       </c>
-      <c r="P18">
+      <c r="AB18">
         <v>69</v>
       </c>
-      <c r="Q18">
+      <c r="AC18">
         <v>117</v>
       </c>
-      <c r="R18">
+      <c r="AD18">
         <v>280</v>
       </c>
-      <c r="S18">
+      <c r="AE18">
         <v>12</v>
       </c>
-      <c r="T18">
+      <c r="AF18">
         <v>11</v>
       </c>
-      <c r="U18">
+      <c r="AG18">
         <v>137</v>
       </c>
-      <c r="V18">
-        <v>0</v>
-      </c>
-      <c r="W18">
+      <c r="AH18">
+        <v>0</v>
+      </c>
+      <c r="AI18">
         <v>2</v>
       </c>
-      <c r="X18">
-        <v>0</v>
-      </c>
-      <c r="Y18">
-        <v>0</v>
-      </c>
-      <c r="Z18">
+      <c r="AJ18">
+        <v>0</v>
+      </c>
+      <c r="AK18">
+        <v>0</v>
+      </c>
+      <c r="AL18">
         <v>3</v>
       </c>
-      <c r="AA18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:27">
+      <c r="AM18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:39">
       <c r="A19" s="1" t="s">
         <v>31</v>
       </c>
@@ -6065,79 +6755,115 @@
         <v>22</v>
       </c>
       <c r="D19">
-        <v>1462</v>
+        <v>606</v>
       </c>
       <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>14</v>
+      </c>
+      <c r="G19">
+        <v>5</v>
+      </c>
+      <c r="H19">
+        <v>85</v>
+      </c>
+      <c r="I19">
+        <v>13</v>
+      </c>
+      <c r="J19">
+        <v>685</v>
+      </c>
+      <c r="K19">
+        <v>54</v>
+      </c>
+      <c r="L19">
         <v>55</v>
       </c>
-      <c r="F19">
+      <c r="M19">
         <v>610</v>
       </c>
-      <c r="G19">
+      <c r="N19">
         <v>48</v>
       </c>
-      <c r="H19">
+      <c r="O19">
         <v>102</v>
       </c>
-      <c r="I19">
-        <v>377</v>
-      </c>
-      <c r="J19">
+      <c r="P19">
+        <v>0</v>
+      </c>
+      <c r="Q19">
+        <v>78</v>
+      </c>
+      <c r="R19">
+        <v>87</v>
+      </c>
+      <c r="S19">
+        <v>61</v>
+      </c>
+      <c r="T19">
+        <v>102</v>
+      </c>
+      <c r="U19">
+        <v>49</v>
+      </c>
+      <c r="V19">
         <v>401</v>
       </c>
-      <c r="K19">
+      <c r="W19">
         <v>61</v>
       </c>
-      <c r="L19">
+      <c r="X19">
         <v>198</v>
       </c>
-      <c r="M19">
+      <c r="Y19">
         <v>57</v>
       </c>
-      <c r="N19">
+      <c r="Z19">
         <v>72</v>
       </c>
-      <c r="O19">
+      <c r="AA19">
         <v>206</v>
       </c>
-      <c r="P19">
+      <c r="AB19">
         <v>39</v>
       </c>
-      <c r="Q19">
+      <c r="AC19">
         <v>79</v>
       </c>
-      <c r="R19">
+      <c r="AD19">
         <v>59</v>
       </c>
-      <c r="S19">
+      <c r="AE19">
         <v>13</v>
       </c>
-      <c r="T19">
+      <c r="AF19">
         <v>17</v>
       </c>
-      <c r="U19">
+      <c r="AG19">
         <v>10</v>
       </c>
-      <c r="V19">
+      <c r="AH19">
         <v>48</v>
       </c>
-      <c r="W19">
+      <c r="AI19">
         <v>96</v>
       </c>
-      <c r="X19">
+      <c r="AJ19">
         <v>2</v>
       </c>
-      <c r="Y19">
+      <c r="AK19">
         <v>111</v>
       </c>
-      <c r="Z19">
+      <c r="AL19">
         <v>2077</v>
       </c>
-      <c r="AA19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:27">
+      <c r="AM19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:39">
       <c r="A20" s="1" t="s">
         <v>32</v>
       </c>
@@ -6148,79 +6874,115 @@
         <v>125</v>
       </c>
       <c r="D20">
-        <v>1370</v>
+        <v>10</v>
       </c>
       <c r="E20">
+        <v>1033</v>
+      </c>
+      <c r="F20">
+        <v>56</v>
+      </c>
+      <c r="G20">
+        <v>185</v>
+      </c>
+      <c r="H20">
+        <v>16</v>
+      </c>
+      <c r="I20">
+        <v>38</v>
+      </c>
+      <c r="J20">
+        <v>14</v>
+      </c>
+      <c r="K20">
+        <v>18</v>
+      </c>
+      <c r="L20">
         <v>41</v>
       </c>
-      <c r="F20">
+      <c r="M20">
         <v>242</v>
       </c>
-      <c r="G20">
+      <c r="N20">
         <v>27</v>
       </c>
-      <c r="H20">
+      <c r="O20">
         <v>231</v>
       </c>
-      <c r="I20">
-        <v>415</v>
-      </c>
-      <c r="J20">
+      <c r="P20">
+        <v>68</v>
+      </c>
+      <c r="Q20">
+        <v>22</v>
+      </c>
+      <c r="R20">
+        <v>108</v>
+      </c>
+      <c r="S20">
+        <v>169</v>
+      </c>
+      <c r="T20">
+        <v>5</v>
+      </c>
+      <c r="U20">
+        <v>43</v>
+      </c>
+      <c r="V20">
         <v>1605</v>
       </c>
-      <c r="K20">
+      <c r="W20">
         <v>14</v>
       </c>
-      <c r="L20">
+      <c r="X20">
         <v>150</v>
       </c>
-      <c r="M20">
+      <c r="Y20">
         <v>59</v>
       </c>
-      <c r="N20">
+      <c r="Z20">
         <v>17</v>
       </c>
-      <c r="O20">
+      <c r="AA20">
         <v>3</v>
       </c>
-      <c r="P20">
+      <c r="AB20">
         <v>61</v>
       </c>
-      <c r="Q20">
+      <c r="AC20">
         <v>2</v>
       </c>
-      <c r="R20">
+      <c r="AD20">
         <v>102</v>
       </c>
-      <c r="S20">
+      <c r="AE20">
         <v>88</v>
       </c>
-      <c r="T20">
+      <c r="AF20">
         <v>1305</v>
       </c>
-      <c r="U20">
+      <c r="AG20">
         <v>42</v>
       </c>
-      <c r="V20">
-        <v>0</v>
-      </c>
-      <c r="W20">
-        <v>0</v>
-      </c>
-      <c r="X20">
+      <c r="AH20">
+        <v>0</v>
+      </c>
+      <c r="AI20">
+        <v>0</v>
+      </c>
+      <c r="AJ20">
         <v>1261</v>
       </c>
-      <c r="Y20">
+      <c r="AK20">
         <v>2</v>
       </c>
-      <c r="Z20">
+      <c r="AL20">
         <v>10</v>
       </c>
-      <c r="AA20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:27">
+      <c r="AM20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:39">
       <c r="A21" s="1" t="s">
         <v>33</v>
       </c>
@@ -6231,79 +6993,115 @@
         <v>0</v>
       </c>
       <c r="D21">
-        <v>1149</v>
+        <v>70</v>
       </c>
       <c r="E21">
+        <v>580</v>
+      </c>
+      <c r="F21">
+        <v>329</v>
+      </c>
+      <c r="G21">
+        <v>49</v>
+      </c>
+      <c r="H21">
+        <v>40</v>
+      </c>
+      <c r="I21">
+        <v>23</v>
+      </c>
+      <c r="J21">
+        <v>49</v>
+      </c>
+      <c r="K21">
+        <v>9</v>
+      </c>
+      <c r="L21">
         <v>8</v>
       </c>
-      <c r="F21">
+      <c r="M21">
         <v>38</v>
       </c>
-      <c r="G21">
+      <c r="N21">
         <v>13</v>
       </c>
-      <c r="H21">
+      <c r="O21">
         <v>28</v>
       </c>
-      <c r="I21">
-        <v>865</v>
-      </c>
-      <c r="J21">
+      <c r="P21">
+        <v>5</v>
+      </c>
+      <c r="Q21">
+        <v>62</v>
+      </c>
+      <c r="R21">
+        <v>105</v>
+      </c>
+      <c r="S21">
+        <v>549</v>
+      </c>
+      <c r="T21">
+        <v>9</v>
+      </c>
+      <c r="U21">
+        <v>135</v>
+      </c>
+      <c r="V21">
         <v>1130</v>
       </c>
-      <c r="K21">
-        <v>1</v>
-      </c>
-      <c r="L21">
+      <c r="W21">
+        <v>1</v>
+      </c>
+      <c r="X21">
         <v>100</v>
       </c>
-      <c r="M21">
+      <c r="Y21">
         <v>2</v>
       </c>
-      <c r="N21">
+      <c r="Z21">
         <v>6</v>
       </c>
-      <c r="O21">
+      <c r="AA21">
         <v>2</v>
       </c>
-      <c r="P21">
+      <c r="AB21">
         <v>2</v>
       </c>
-      <c r="Q21">
+      <c r="AC21">
         <v>2</v>
       </c>
-      <c r="R21">
+      <c r="AD21">
         <v>203</v>
       </c>
-      <c r="S21">
+      <c r="AE21">
         <v>37</v>
       </c>
-      <c r="T21">
+      <c r="AF21">
         <v>871</v>
       </c>
-      <c r="U21">
-        <v>1</v>
-      </c>
-      <c r="V21">
+      <c r="AG21">
+        <v>1</v>
+      </c>
+      <c r="AH21">
         <v>3</v>
       </c>
-      <c r="W21">
+      <c r="AI21">
         <v>164</v>
       </c>
-      <c r="X21">
+      <c r="AJ21">
         <v>127</v>
       </c>
-      <c r="Y21">
-        <v>0</v>
-      </c>
-      <c r="Z21">
-        <v>0</v>
-      </c>
-      <c r="AA21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:27">
+      <c r="AK21">
+        <v>0</v>
+      </c>
+      <c r="AL21">
+        <v>0</v>
+      </c>
+      <c r="AM21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:39">
       <c r="A22" s="1" t="s">
         <v>34</v>
       </c>
@@ -6314,79 +7112,115 @@
         <v>82</v>
       </c>
       <c r="D22">
-        <v>1155</v>
+        <v>54</v>
       </c>
       <c r="E22">
+        <v>286</v>
+      </c>
+      <c r="F22">
+        <v>173</v>
+      </c>
+      <c r="G22">
+        <v>123</v>
+      </c>
+      <c r="H22">
+        <v>39</v>
+      </c>
+      <c r="I22">
+        <v>94</v>
+      </c>
+      <c r="J22">
+        <v>275</v>
+      </c>
+      <c r="K22">
+        <v>111</v>
+      </c>
+      <c r="L22">
         <v>30</v>
       </c>
-      <c r="F22">
+      <c r="M22">
         <v>89</v>
       </c>
-      <c r="G22">
+      <c r="N22">
         <v>28</v>
       </c>
-      <c r="H22">
+      <c r="O22">
         <v>105</v>
       </c>
-      <c r="I22">
-        <v>718</v>
-      </c>
-      <c r="J22">
+      <c r="P22">
+        <v>1</v>
+      </c>
+      <c r="Q22">
+        <v>15</v>
+      </c>
+      <c r="R22">
+        <v>215</v>
+      </c>
+      <c r="S22">
+        <v>292</v>
+      </c>
+      <c r="T22">
+        <v>26</v>
+      </c>
+      <c r="U22">
+        <v>169</v>
+      </c>
+      <c r="V22">
         <v>734</v>
       </c>
-      <c r="K22">
+      <c r="W22">
         <v>27</v>
       </c>
-      <c r="L22">
+      <c r="X22">
         <v>52</v>
       </c>
-      <c r="M22">
+      <c r="Y22">
         <v>47</v>
       </c>
-      <c r="N22">
+      <c r="Z22">
         <v>19</v>
       </c>
-      <c r="O22">
+      <c r="AA22">
         <v>5</v>
       </c>
-      <c r="P22">
+      <c r="AB22">
         <v>23</v>
       </c>
-      <c r="Q22">
+      <c r="AC22">
         <v>5</v>
       </c>
-      <c r="R22">
+      <c r="AD22">
         <v>218</v>
       </c>
-      <c r="S22">
+      <c r="AE22">
         <v>32</v>
       </c>
-      <c r="T22">
+      <c r="AF22">
         <v>466</v>
       </c>
-      <c r="U22">
+      <c r="AG22">
         <v>42</v>
       </c>
-      <c r="V22">
+      <c r="AH22">
         <v>24</v>
       </c>
-      <c r="W22">
+      <c r="AI22">
         <v>5</v>
       </c>
-      <c r="X22">
+      <c r="AJ22">
         <v>5</v>
       </c>
-      <c r="Y22">
+      <c r="AK22">
         <v>20</v>
       </c>
-      <c r="Z22">
+      <c r="AL22">
         <v>567</v>
       </c>
-      <c r="AA22">
+      <c r="AM22">
         <v>26</v>
       </c>
     </row>
-    <row r="23" spans="1:27">
+    <row r="23" spans="1:39">
       <c r="A23" s="1" t="s">
         <v>35</v>
       </c>
@@ -6397,79 +7231,115 @@
         <v>35</v>
       </c>
       <c r="D23">
-        <v>508</v>
+        <v>3</v>
       </c>
       <c r="E23">
+        <v>93</v>
+      </c>
+      <c r="F23">
+        <v>144</v>
+      </c>
+      <c r="G23">
+        <v>54</v>
+      </c>
+      <c r="H23">
+        <v>9</v>
+      </c>
+      <c r="I23">
+        <v>23</v>
+      </c>
+      <c r="J23">
+        <v>124</v>
+      </c>
+      <c r="K23">
+        <v>58</v>
+      </c>
+      <c r="L23">
         <v>15</v>
       </c>
-      <c r="F23">
+      <c r="M23">
         <v>46</v>
       </c>
-      <c r="G23">
+      <c r="N23">
         <v>7</v>
       </c>
-      <c r="H23">
+      <c r="O23">
         <v>44</v>
       </c>
-      <c r="I23">
-        <v>755</v>
-      </c>
-      <c r="J23">
+      <c r="P23">
+        <v>3</v>
+      </c>
+      <c r="Q23">
+        <v>32</v>
+      </c>
+      <c r="R23">
+        <v>149</v>
+      </c>
+      <c r="S23">
+        <v>360</v>
+      </c>
+      <c r="T23">
+        <v>20</v>
+      </c>
+      <c r="U23">
+        <v>191</v>
+      </c>
+      <c r="V23">
         <v>1025</v>
       </c>
-      <c r="K23">
+      <c r="W23">
         <v>9</v>
       </c>
-      <c r="L23">
+      <c r="X23">
         <v>62</v>
       </c>
-      <c r="M23">
+      <c r="Y23">
         <v>13</v>
       </c>
-      <c r="N23">
+      <c r="Z23">
         <v>2</v>
       </c>
-      <c r="O23">
-        <v>0</v>
-      </c>
-      <c r="P23">
+      <c r="AA23">
+        <v>0</v>
+      </c>
+      <c r="AB23">
         <v>7</v>
       </c>
-      <c r="Q23">
+      <c r="AC23">
         <v>3</v>
       </c>
-      <c r="R23">
+      <c r="AD23">
         <v>219</v>
       </c>
-      <c r="S23">
+      <c r="AE23">
         <v>20</v>
       </c>
-      <c r="T23">
+      <c r="AF23">
         <v>991</v>
       </c>
-      <c r="U23">
+      <c r="AG23">
         <v>5</v>
       </c>
-      <c r="V23">
+      <c r="AH23">
         <v>13</v>
       </c>
-      <c r="W23">
-        <v>0</v>
-      </c>
-      <c r="X23">
+      <c r="AI23">
+        <v>0</v>
+      </c>
+      <c r="AJ23">
         <v>2</v>
       </c>
-      <c r="Y23">
-        <v>1</v>
-      </c>
-      <c r="Z23">
+      <c r="AK23">
+        <v>1</v>
+      </c>
+      <c r="AL23">
         <v>231</v>
       </c>
-      <c r="AA23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:27">
+      <c r="AM23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:39">
       <c r="A24" s="1" t="s">
         <v>36</v>
       </c>
@@ -6480,79 +7350,115 @@
         <v>16</v>
       </c>
       <c r="D24">
-        <v>696</v>
+        <v>8</v>
       </c>
       <c r="E24">
+        <v>156</v>
+      </c>
+      <c r="F24">
+        <v>111</v>
+      </c>
+      <c r="G24">
+        <v>119</v>
+      </c>
+      <c r="H24">
+        <v>21</v>
+      </c>
+      <c r="I24">
+        <v>79</v>
+      </c>
+      <c r="J24">
+        <v>149</v>
+      </c>
+      <c r="K24">
+        <v>53</v>
+      </c>
+      <c r="L24">
         <v>9</v>
       </c>
-      <c r="F24">
+      <c r="M24">
         <v>46</v>
       </c>
-      <c r="G24">
+      <c r="N24">
         <v>10</v>
       </c>
-      <c r="H24">
+      <c r="O24">
         <v>33</v>
       </c>
-      <c r="I24">
-        <v>1502</v>
-      </c>
-      <c r="J24">
+      <c r="P24">
+        <v>0</v>
+      </c>
+      <c r="Q24">
+        <v>35</v>
+      </c>
+      <c r="R24">
+        <v>294</v>
+      </c>
+      <c r="S24">
+        <v>744</v>
+      </c>
+      <c r="T24">
+        <v>67</v>
+      </c>
+      <c r="U24">
+        <v>362</v>
+      </c>
+      <c r="V24">
         <v>596</v>
       </c>
-      <c r="K24">
+      <c r="W24">
         <v>16</v>
       </c>
-      <c r="L24">
+      <c r="X24">
         <v>17</v>
-      </c>
-      <c r="M24">
-        <v>32</v>
-      </c>
-      <c r="N24">
-        <v>6</v>
-      </c>
-      <c r="O24">
-        <v>1</v>
-      </c>
-      <c r="P24">
-        <v>16</v>
-      </c>
-      <c r="Q24">
-        <v>3</v>
-      </c>
-      <c r="R24">
-        <v>257</v>
-      </c>
-      <c r="S24">
-        <v>15</v>
-      </c>
-      <c r="T24">
-        <v>354</v>
-      </c>
-      <c r="U24">
-        <v>14</v>
-      </c>
-      <c r="V24">
-        <v>12</v>
-      </c>
-      <c r="W24">
-        <v>0</v>
-      </c>
-      <c r="X24">
-        <v>3</v>
       </c>
       <c r="Y24">
         <v>32</v>
       </c>
       <c r="Z24">
+        <v>6</v>
+      </c>
+      <c r="AA24">
+        <v>1</v>
+      </c>
+      <c r="AB24">
+        <v>16</v>
+      </c>
+      <c r="AC24">
+        <v>3</v>
+      </c>
+      <c r="AD24">
+        <v>257</v>
+      </c>
+      <c r="AE24">
+        <v>15</v>
+      </c>
+      <c r="AF24">
+        <v>354</v>
+      </c>
+      <c r="AG24">
+        <v>14</v>
+      </c>
+      <c r="AH24">
+        <v>12</v>
+      </c>
+      <c r="AI24">
+        <v>0</v>
+      </c>
+      <c r="AJ24">
+        <v>3</v>
+      </c>
+      <c r="AK24">
+        <v>32</v>
+      </c>
+      <c r="AL24">
         <v>211</v>
       </c>
-      <c r="AA24">
+      <c r="AM24">
         <v>18</v>
       </c>
     </row>
-    <row r="25" spans="1:27">
+    <row r="25" spans="1:39">
       <c r="A25" s="1" t="s">
         <v>37</v>
       </c>
@@ -6563,79 +7469,115 @@
         <v>10</v>
       </c>
       <c r="D25">
-        <v>971</v>
+        <v>7</v>
       </c>
       <c r="E25">
+        <v>287</v>
+      </c>
+      <c r="F25">
+        <v>18</v>
+      </c>
+      <c r="G25">
+        <v>424</v>
+      </c>
+      <c r="H25">
+        <v>20</v>
+      </c>
+      <c r="I25">
+        <v>104</v>
+      </c>
+      <c r="J25">
+        <v>2</v>
+      </c>
+      <c r="K25">
+        <v>109</v>
+      </c>
+      <c r="L25">
         <v>4</v>
       </c>
-      <c r="F25">
+      <c r="M25">
         <v>47</v>
       </c>
-      <c r="G25">
+      <c r="N25">
         <v>7</v>
       </c>
-      <c r="H25">
+      <c r="O25">
         <v>49</v>
       </c>
-      <c r="I25">
-        <v>325</v>
-      </c>
-      <c r="J25">
+      <c r="P25">
+        <v>119</v>
+      </c>
+      <c r="Q25">
+        <v>39</v>
+      </c>
+      <c r="R25">
+        <v>50</v>
+      </c>
+      <c r="S25">
+        <v>61</v>
+      </c>
+      <c r="T25">
+        <v>15</v>
+      </c>
+      <c r="U25">
+        <v>41</v>
+      </c>
+      <c r="V25">
         <v>425</v>
       </c>
-      <c r="K25">
+      <c r="W25">
         <v>25</v>
       </c>
-      <c r="L25">
+      <c r="X25">
         <v>13</v>
       </c>
-      <c r="M25">
+      <c r="Y25">
         <v>86</v>
       </c>
-      <c r="N25">
+      <c r="Z25">
         <v>23</v>
       </c>
-      <c r="O25">
+      <c r="AA25">
         <v>6</v>
       </c>
-      <c r="P25">
+      <c r="AB25">
         <v>9</v>
       </c>
-      <c r="Q25">
+      <c r="AC25">
         <v>11</v>
       </c>
-      <c r="R25">
+      <c r="AD25">
         <v>113</v>
       </c>
-      <c r="S25">
+      <c r="AE25">
         <v>40</v>
       </c>
-      <c r="T25">
+      <c r="AF25">
         <v>254</v>
       </c>
-      <c r="U25">
+      <c r="AG25">
         <v>29</v>
       </c>
-      <c r="V25">
+      <c r="AH25">
         <v>77</v>
       </c>
-      <c r="W25">
-        <v>1</v>
-      </c>
-      <c r="X25">
+      <c r="AI25">
+        <v>1</v>
+      </c>
+      <c r="AJ25">
         <v>2</v>
       </c>
-      <c r="Y25">
+      <c r="AK25">
         <v>1175</v>
       </c>
-      <c r="Z25">
+      <c r="AL25">
         <v>7</v>
       </c>
-      <c r="AA25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:27">
+      <c r="AM25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:39">
       <c r="A26" s="1" t="s">
         <v>38</v>
       </c>
@@ -6646,79 +7588,115 @@
         <v>81</v>
       </c>
       <c r="D26">
-        <v>2897</v>
+        <v>14</v>
       </c>
       <c r="E26">
+        <v>42</v>
+      </c>
+      <c r="F26">
         <v>23</v>
       </c>
-      <c r="F26">
+      <c r="G26">
+        <v>920</v>
+      </c>
+      <c r="H26">
+        <v>36</v>
+      </c>
+      <c r="I26">
+        <v>1704</v>
+      </c>
+      <c r="J26">
+        <v>117</v>
+      </c>
+      <c r="K26">
+        <v>41</v>
+      </c>
+      <c r="L26">
+        <v>23</v>
+      </c>
+      <c r="M26">
         <v>246</v>
       </c>
-      <c r="G26">
+      <c r="N26">
         <v>27</v>
       </c>
-      <c r="H26">
+      <c r="O26">
         <v>243</v>
       </c>
-      <c r="I26">
-        <v>2366</v>
-      </c>
-      <c r="J26">
+      <c r="P26">
+        <v>82</v>
+      </c>
+      <c r="Q26">
+        <v>99</v>
+      </c>
+      <c r="R26">
+        <v>300</v>
+      </c>
+      <c r="S26">
+        <v>1417</v>
+      </c>
+      <c r="T26">
+        <v>47</v>
+      </c>
+      <c r="U26">
+        <v>421</v>
+      </c>
+      <c r="V26">
         <v>209</v>
       </c>
-      <c r="K26">
+      <c r="W26">
         <v>64</v>
       </c>
-      <c r="L26">
+      <c r="X26">
         <v>32</v>
       </c>
-      <c r="M26">
+      <c r="Y26">
         <v>176</v>
       </c>
-      <c r="N26">
+      <c r="Z26">
         <v>20</v>
       </c>
-      <c r="O26">
+      <c r="AA26">
         <v>2</v>
       </c>
-      <c r="P26">
+      <c r="AB26">
         <v>41</v>
       </c>
-      <c r="Q26">
+      <c r="AC26">
         <v>2</v>
       </c>
-      <c r="R26">
+      <c r="AD26">
         <v>377</v>
       </c>
-      <c r="S26">
+      <c r="AE26">
         <v>93</v>
       </c>
-      <c r="T26">
+      <c r="AF26">
         <v>124</v>
       </c>
-      <c r="U26">
+      <c r="AG26">
         <v>94</v>
       </c>
-      <c r="V26">
+      <c r="AH26">
         <v>7</v>
       </c>
-      <c r="W26">
+      <c r="AI26">
         <v>7</v>
       </c>
-      <c r="X26">
-        <v>1</v>
-      </c>
-      <c r="Y26">
+      <c r="AJ26">
+        <v>1</v>
+      </c>
+      <c r="AK26">
         <v>18</v>
       </c>
-      <c r="Z26">
+      <c r="AL26">
         <v>433</v>
       </c>
-      <c r="AA26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:27">
+      <c r="AM26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:39">
       <c r="A27" s="1" t="s">
         <v>39</v>
       </c>
@@ -6729,79 +7707,115 @@
         <v>1</v>
       </c>
       <c r="D27">
-        <v>163</v>
+        <v>8</v>
       </c>
       <c r="E27">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27">
+        <v>84</v>
+      </c>
+      <c r="H27">
+        <v>8</v>
+      </c>
+      <c r="I27">
+        <v>8</v>
+      </c>
+      <c r="J27">
+        <v>1</v>
+      </c>
+      <c r="K27">
+        <v>2</v>
+      </c>
+      <c r="L27">
+        <v>0</v>
+      </c>
+      <c r="M27">
         <v>40</v>
       </c>
-      <c r="G27">
-        <v>0</v>
-      </c>
-      <c r="H27">
+      <c r="N27">
+        <v>0</v>
+      </c>
+      <c r="O27">
         <v>23</v>
       </c>
-      <c r="I27">
-        <v>369</v>
-      </c>
-      <c r="J27">
+      <c r="P27">
+        <v>120</v>
+      </c>
+      <c r="Q27">
+        <v>5</v>
+      </c>
+      <c r="R27">
+        <v>44</v>
+      </c>
+      <c r="S27">
+        <v>98</v>
+      </c>
+      <c r="T27">
+        <v>1</v>
+      </c>
+      <c r="U27">
+        <v>101</v>
+      </c>
+      <c r="V27">
         <v>709</v>
       </c>
-      <c r="K27">
+      <c r="W27">
         <v>8</v>
       </c>
-      <c r="L27">
+      <c r="X27">
         <v>28</v>
       </c>
-      <c r="M27">
+      <c r="Y27">
         <v>3</v>
       </c>
-      <c r="N27">
-        <v>1</v>
-      </c>
-      <c r="O27">
-        <v>0</v>
-      </c>
-      <c r="P27">
-        <v>1</v>
-      </c>
-      <c r="Q27">
-        <v>1</v>
-      </c>
-      <c r="R27">
+      <c r="Z27">
+        <v>1</v>
+      </c>
+      <c r="AA27">
+        <v>0</v>
+      </c>
+      <c r="AB27">
+        <v>1</v>
+      </c>
+      <c r="AC27">
+        <v>1</v>
+      </c>
+      <c r="AD27">
         <v>63</v>
       </c>
-      <c r="S27">
-        <v>0</v>
-      </c>
-      <c r="T27">
+      <c r="AE27">
+        <v>0</v>
+      </c>
+      <c r="AF27">
         <v>782</v>
       </c>
-      <c r="U27">
+      <c r="AG27">
         <v>11</v>
       </c>
-      <c r="V27">
+      <c r="AH27">
         <v>2</v>
       </c>
-      <c r="W27">
+      <c r="AI27">
         <v>14</v>
       </c>
-      <c r="X27">
+      <c r="AJ27">
         <v>8</v>
       </c>
-      <c r="Y27">
+      <c r="AK27">
         <v>408</v>
       </c>
-      <c r="Z27">
+      <c r="AL27">
         <v>210</v>
       </c>
-      <c r="AA27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:27">
+      <c r="AM27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:39">
       <c r="A28" s="1" t="s">
         <v>40</v>
       </c>
@@ -6812,79 +7826,115 @@
         <v>234</v>
       </c>
       <c r="D28">
-        <v>983</v>
+        <v>188</v>
       </c>
       <c r="E28">
+        <v>26</v>
+      </c>
+      <c r="F28">
+        <v>157</v>
+      </c>
+      <c r="G28">
+        <v>84</v>
+      </c>
+      <c r="H28">
+        <v>70</v>
+      </c>
+      <c r="I28">
+        <v>9</v>
+      </c>
+      <c r="J28">
+        <v>305</v>
+      </c>
+      <c r="K28">
+        <v>144</v>
+      </c>
+      <c r="L28">
         <v>88</v>
       </c>
-      <c r="F28">
+      <c r="M28">
         <v>309</v>
       </c>
-      <c r="G28">
+      <c r="N28">
         <v>91</v>
       </c>
-      <c r="H28">
+      <c r="O28">
         <v>242</v>
       </c>
-      <c r="I28">
-        <v>537</v>
-      </c>
-      <c r="J28">
+      <c r="P28">
+        <v>9</v>
+      </c>
+      <c r="Q28">
+        <v>36</v>
+      </c>
+      <c r="R28">
+        <v>164</v>
+      </c>
+      <c r="S28">
+        <v>167</v>
+      </c>
+      <c r="T28">
+        <v>84</v>
+      </c>
+      <c r="U28">
+        <v>77</v>
+      </c>
+      <c r="V28">
         <v>154</v>
       </c>
-      <c r="K28">
+      <c r="W28">
         <v>55</v>
       </c>
-      <c r="L28">
+      <c r="X28">
         <v>47</v>
       </c>
-      <c r="M28">
+      <c r="Y28">
         <v>55</v>
       </c>
-      <c r="N28">
+      <c r="Z28">
         <v>62</v>
       </c>
-      <c r="O28">
+      <c r="AA28">
         <v>736</v>
       </c>
-      <c r="P28">
+      <c r="AB28">
         <v>10</v>
       </c>
-      <c r="Q28">
+      <c r="AC28">
         <v>367</v>
       </c>
-      <c r="R28">
+      <c r="AD28">
         <v>168</v>
       </c>
-      <c r="S28">
+      <c r="AE28">
         <v>45</v>
       </c>
-      <c r="T28">
+      <c r="AF28">
         <v>75</v>
       </c>
-      <c r="U28">
+      <c r="AG28">
         <v>27</v>
       </c>
-      <c r="V28">
+      <c r="AH28">
         <v>279</v>
       </c>
-      <c r="W28">
+      <c r="AI28">
         <v>104</v>
       </c>
-      <c r="X28">
-        <v>0</v>
-      </c>
-      <c r="Y28">
+      <c r="AJ28">
+        <v>0</v>
+      </c>
+      <c r="AK28">
         <v>841</v>
       </c>
-      <c r="Z28">
+      <c r="AL28">
         <v>64</v>
       </c>
-      <c r="AA28">
+      <c r="AM28">
         <v>9</v>
       </c>
     </row>
-    <row r="29" spans="1:27">
+    <row r="29" spans="1:39">
       <c r="A29" s="1" t="s">
         <v>41</v>
       </c>
@@ -6895,79 +7945,115 @@
         <v>7</v>
       </c>
       <c r="D29">
-        <v>1107</v>
+        <v>6</v>
       </c>
       <c r="E29">
+        <v>416</v>
+      </c>
+      <c r="F29">
+        <v>38</v>
+      </c>
+      <c r="G29">
+        <v>457</v>
+      </c>
+      <c r="H29">
+        <v>22</v>
+      </c>
+      <c r="I29">
+        <v>116</v>
+      </c>
+      <c r="J29">
+        <v>36</v>
+      </c>
+      <c r="K29">
+        <v>16</v>
+      </c>
+      <c r="L29">
         <v>7</v>
       </c>
-      <c r="F29">
+      <c r="M29">
         <v>74</v>
       </c>
-      <c r="G29">
+      <c r="N29">
         <v>10</v>
       </c>
-      <c r="H29">
+      <c r="O29">
         <v>63</v>
       </c>
-      <c r="I29">
-        <v>1915</v>
-      </c>
-      <c r="J29">
+      <c r="P29">
+        <v>56</v>
+      </c>
+      <c r="Q29">
+        <v>132</v>
+      </c>
+      <c r="R29">
+        <v>231</v>
+      </c>
+      <c r="S29">
+        <v>688</v>
+      </c>
+      <c r="T29">
+        <v>94</v>
+      </c>
+      <c r="U29">
+        <v>714</v>
+      </c>
+      <c r="V29">
         <v>809</v>
       </c>
-      <c r="K29">
+      <c r="W29">
         <v>6</v>
       </c>
-      <c r="L29">
+      <c r="X29">
         <v>48</v>
       </c>
-      <c r="M29">
+      <c r="Y29">
         <v>21</v>
       </c>
-      <c r="N29">
+      <c r="Z29">
         <v>4</v>
-      </c>
-      <c r="O29">
-        <v>2</v>
-      </c>
-      <c r="P29">
-        <v>8</v>
-      </c>
-      <c r="Q29">
-        <v>2</v>
-      </c>
-      <c r="R29">
-        <v>254</v>
-      </c>
-      <c r="S29">
-        <v>14</v>
-      </c>
-      <c r="T29">
-        <v>2788</v>
-      </c>
-      <c r="U29">
-        <v>46</v>
-      </c>
-      <c r="V29">
-        <v>7</v>
-      </c>
-      <c r="W29">
-        <v>3</v>
-      </c>
-      <c r="X29">
-        <v>216</v>
-      </c>
-      <c r="Y29">
-        <v>75</v>
-      </c>
-      <c r="Z29">
-        <v>134</v>
       </c>
       <c r="AA29">
         <v>2</v>
       </c>
-    </row>
-    <row r="30" spans="1:27">
+      <c r="AB29">
+        <v>8</v>
+      </c>
+      <c r="AC29">
+        <v>2</v>
+      </c>
+      <c r="AD29">
+        <v>254</v>
+      </c>
+      <c r="AE29">
+        <v>14</v>
+      </c>
+      <c r="AF29">
+        <v>2788</v>
+      </c>
+      <c r="AG29">
+        <v>46</v>
+      </c>
+      <c r="AH29">
+        <v>7</v>
+      </c>
+      <c r="AI29">
+        <v>3</v>
+      </c>
+      <c r="AJ29">
+        <v>216</v>
+      </c>
+      <c r="AK29">
+        <v>75</v>
+      </c>
+      <c r="AL29">
+        <v>134</v>
+      </c>
+      <c r="AM29">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:39">
       <c r="A30" s="1" t="s">
         <v>42</v>
       </c>
@@ -6978,79 +8064,115 @@
         <v>1</v>
       </c>
       <c r="D30">
-        <v>889</v>
+        <v>2</v>
       </c>
       <c r="E30">
+        <v>80</v>
+      </c>
+      <c r="F30">
+        <v>11</v>
+      </c>
+      <c r="G30">
+        <v>645</v>
+      </c>
+      <c r="H30">
+        <v>6</v>
+      </c>
+      <c r="I30">
+        <v>139</v>
+      </c>
+      <c r="J30">
+        <v>1</v>
+      </c>
+      <c r="K30">
+        <v>5</v>
+      </c>
+      <c r="L30">
         <v>4</v>
       </c>
-      <c r="F30">
+      <c r="M30">
         <v>82</v>
       </c>
-      <c r="G30">
+      <c r="N30">
         <v>5</v>
       </c>
-      <c r="H30">
+      <c r="O30">
         <v>43</v>
       </c>
-      <c r="I30">
-        <v>1128</v>
-      </c>
-      <c r="J30">
+      <c r="P30">
+        <v>84</v>
+      </c>
+      <c r="Q30">
+        <v>38</v>
+      </c>
+      <c r="R30">
+        <v>300</v>
+      </c>
+      <c r="S30">
+        <v>427</v>
+      </c>
+      <c r="T30">
+        <v>15</v>
+      </c>
+      <c r="U30">
+        <v>264</v>
+      </c>
+      <c r="V30">
         <v>1209</v>
-      </c>
-      <c r="K30">
-        <v>2</v>
-      </c>
-      <c r="L30">
-        <v>34</v>
-      </c>
-      <c r="M30">
-        <v>14</v>
-      </c>
-      <c r="N30">
-        <v>0</v>
-      </c>
-      <c r="O30">
-        <v>11</v>
-      </c>
-      <c r="P30">
-        <v>11</v>
-      </c>
-      <c r="Q30">
-        <v>5</v>
-      </c>
-      <c r="R30">
-        <v>55</v>
-      </c>
-      <c r="S30">
-        <v>3</v>
-      </c>
-      <c r="T30">
-        <v>3033</v>
-      </c>
-      <c r="U30">
-        <v>11</v>
-      </c>
-      <c r="V30">
-        <v>6</v>
       </c>
       <c r="W30">
         <v>2</v>
       </c>
       <c r="X30">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="Y30">
+        <v>14</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+      <c r="AA30">
+        <v>11</v>
+      </c>
+      <c r="AB30">
+        <v>11</v>
+      </c>
+      <c r="AC30">
+        <v>5</v>
+      </c>
+      <c r="AD30">
+        <v>55</v>
+      </c>
+      <c r="AE30">
+        <v>3</v>
+      </c>
+      <c r="AF30">
+        <v>3033</v>
+      </c>
+      <c r="AG30">
+        <v>11</v>
+      </c>
+      <c r="AH30">
+        <v>6</v>
+      </c>
+      <c r="AI30">
+        <v>2</v>
+      </c>
+      <c r="AJ30">
+        <v>0</v>
+      </c>
+      <c r="AK30">
         <v>268</v>
       </c>
-      <c r="Z30">
+      <c r="AL30">
         <v>212</v>
       </c>
-      <c r="AA30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:27">
+      <c r="AM30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:39">
       <c r="A31" s="1" t="s">
         <v>43</v>
       </c>
@@ -7061,79 +8183,115 @@
         <v>28</v>
       </c>
       <c r="D31">
-        <v>2086</v>
+        <v>1566</v>
       </c>
       <c r="E31">
+        <v>30</v>
+      </c>
+      <c r="F31">
+        <v>77</v>
+      </c>
+      <c r="G31">
+        <v>5</v>
+      </c>
+      <c r="H31">
+        <v>75</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>60</v>
+      </c>
+      <c r="K31">
+        <v>273</v>
+      </c>
+      <c r="L31">
         <v>6</v>
       </c>
-      <c r="F31">
+      <c r="M31">
         <v>18</v>
       </c>
-      <c r="G31">
+      <c r="N31">
         <v>7</v>
       </c>
-      <c r="H31">
+      <c r="O31">
         <v>49</v>
       </c>
-      <c r="I31">
-        <v>193</v>
-      </c>
-      <c r="J31">
+      <c r="P31">
+        <v>10</v>
+      </c>
+      <c r="Q31">
+        <v>31</v>
+      </c>
+      <c r="R31">
+        <v>33</v>
+      </c>
+      <c r="S31">
+        <v>11</v>
+      </c>
+      <c r="T31">
+        <v>95</v>
+      </c>
+      <c r="U31">
+        <v>13</v>
+      </c>
+      <c r="V31">
         <v>640</v>
       </c>
-      <c r="K31">
+      <c r="W31">
         <v>50</v>
       </c>
-      <c r="L31">
+      <c r="X31">
         <v>194</v>
       </c>
-      <c r="M31">
+      <c r="Y31">
         <v>6</v>
       </c>
-      <c r="N31">
+      <c r="Z31">
         <v>14</v>
       </c>
-      <c r="O31">
+      <c r="AA31">
         <v>46</v>
       </c>
-      <c r="P31">
+      <c r="AB31">
         <v>13</v>
       </c>
-      <c r="Q31">
+      <c r="AC31">
         <v>3</v>
       </c>
-      <c r="R31">
+      <c r="AD31">
         <v>119</v>
       </c>
-      <c r="S31">
+      <c r="AE31">
         <v>51</v>
       </c>
-      <c r="T31">
+      <c r="AF31">
         <v>182</v>
       </c>
-      <c r="U31">
+      <c r="AG31">
         <v>12</v>
       </c>
-      <c r="V31">
+      <c r="AH31">
         <v>2129</v>
       </c>
-      <c r="W31">
+      <c r="AI31">
         <v>210</v>
       </c>
-      <c r="X31">
+      <c r="AJ31">
         <v>15</v>
       </c>
-      <c r="Y31">
+      <c r="AK31">
         <v>169</v>
       </c>
-      <c r="Z31">
+      <c r="AL31">
         <v>60</v>
       </c>
-      <c r="AA31">
+      <c r="AM31">
         <v>300</v>
       </c>
     </row>
-    <row r="32" spans="1:27">
+    <row r="32" spans="1:39">
       <c r="A32" s="1" t="s">
         <v>44</v>
       </c>
@@ -7144,79 +8302,115 @@
         <v>54</v>
       </c>
       <c r="D32">
-        <v>1309</v>
+        <v>758</v>
       </c>
       <c r="E32">
+        <v>17</v>
+      </c>
+      <c r="F32">
+        <v>166</v>
+      </c>
+      <c r="G32">
+        <v>7</v>
+      </c>
+      <c r="H32">
+        <v>59</v>
+      </c>
+      <c r="I32">
+        <v>3</v>
+      </c>
+      <c r="J32">
+        <v>129</v>
+      </c>
+      <c r="K32">
+        <v>170</v>
+      </c>
+      <c r="L32">
         <v>37</v>
       </c>
-      <c r="F32">
+      <c r="M32">
         <v>93</v>
       </c>
-      <c r="G32">
+      <c r="N32">
         <v>79</v>
       </c>
-      <c r="H32">
+      <c r="O32">
         <v>80</v>
       </c>
-      <c r="I32">
-        <v>125</v>
-      </c>
-      <c r="J32">
+      <c r="P32">
+        <v>2</v>
+      </c>
+      <c r="Q32">
+        <v>13</v>
+      </c>
+      <c r="R32">
+        <v>61</v>
+      </c>
+      <c r="S32">
+        <v>6</v>
+      </c>
+      <c r="T32">
+        <v>31</v>
+      </c>
+      <c r="U32">
+        <v>12</v>
+      </c>
+      <c r="V32">
         <v>522</v>
       </c>
-      <c r="K32">
+      <c r="W32">
         <v>37</v>
       </c>
-      <c r="L32">
+      <c r="X32">
         <v>150</v>
       </c>
-      <c r="M32">
+      <c r="Y32">
         <v>5</v>
       </c>
-      <c r="N32">
+      <c r="Z32">
         <v>31</v>
       </c>
-      <c r="O32">
+      <c r="AA32">
         <v>65</v>
       </c>
-      <c r="P32">
+      <c r="AB32">
         <v>35</v>
       </c>
-      <c r="Q32">
+      <c r="AC32">
         <v>19</v>
       </c>
-      <c r="R32">
+      <c r="AD32">
         <v>76</v>
       </c>
-      <c r="S32">
+      <c r="AE32">
         <v>97</v>
       </c>
-      <c r="T32">
+      <c r="AF32">
         <v>90</v>
       </c>
-      <c r="U32">
+      <c r="AG32">
         <v>10</v>
       </c>
-      <c r="V32">
+      <c r="AH32">
         <v>789</v>
       </c>
-      <c r="W32">
+      <c r="AI32">
         <v>84</v>
       </c>
-      <c r="X32">
-        <v>0</v>
-      </c>
-      <c r="Y32">
+      <c r="AJ32">
+        <v>0</v>
+      </c>
+      <c r="AK32">
         <v>143</v>
       </c>
-      <c r="Z32">
+      <c r="AL32">
         <v>14</v>
       </c>
-      <c r="AA32">
+      <c r="AM32">
         <v>38</v>
       </c>
     </row>
-    <row r="33" spans="1:27">
+    <row r="33" spans="1:39">
       <c r="A33" s="1" t="s">
         <v>45</v>
       </c>
@@ -7227,79 +8421,115 @@
         <v>34</v>
       </c>
       <c r="D33">
-        <v>1053</v>
+        <v>116</v>
       </c>
       <c r="E33">
+        <v>226</v>
+      </c>
+      <c r="F33">
+        <v>150</v>
+      </c>
+      <c r="G33">
+        <v>105</v>
+      </c>
+      <c r="H33">
+        <v>178</v>
+      </c>
+      <c r="I33">
+        <v>37</v>
+      </c>
+      <c r="J33">
+        <v>75</v>
+      </c>
+      <c r="K33">
+        <v>166</v>
+      </c>
+      <c r="L33">
         <v>7</v>
       </c>
-      <c r="F33">
+      <c r="M33">
         <v>69</v>
       </c>
-      <c r="G33">
+      <c r="N33">
         <v>25</v>
       </c>
-      <c r="H33">
+      <c r="O33">
         <v>90</v>
       </c>
-      <c r="I33">
-        <v>337</v>
-      </c>
-      <c r="J33">
+      <c r="P33">
+        <v>25</v>
+      </c>
+      <c r="Q33">
+        <v>124</v>
+      </c>
+      <c r="R33">
+        <v>85</v>
+      </c>
+      <c r="S33">
+        <v>51</v>
+      </c>
+      <c r="T33">
+        <v>26</v>
+      </c>
+      <c r="U33">
+        <v>26</v>
+      </c>
+      <c r="V33">
         <v>892</v>
       </c>
-      <c r="K33">
+      <c r="W33">
         <v>80</v>
       </c>
-      <c r="L33">
+      <c r="X33">
         <v>73</v>
       </c>
-      <c r="M33">
+      <c r="Y33">
         <v>21</v>
       </c>
-      <c r="N33">
+      <c r="Z33">
         <v>19</v>
       </c>
-      <c r="O33">
+      <c r="AA33">
         <v>27</v>
       </c>
-      <c r="P33">
+      <c r="AB33">
         <v>26</v>
       </c>
-      <c r="Q33">
+      <c r="AC33">
         <v>4</v>
       </c>
-      <c r="R33">
+      <c r="AD33">
         <v>71</v>
       </c>
-      <c r="S33">
+      <c r="AE33">
         <v>181</v>
       </c>
-      <c r="T33">
+      <c r="AF33">
         <v>246</v>
       </c>
-      <c r="U33">
+      <c r="AG33">
         <v>12</v>
       </c>
-      <c r="V33">
+      <c r="AH33">
         <v>1162</v>
       </c>
-      <c r="W33">
+      <c r="AI33">
         <v>69</v>
       </c>
-      <c r="X33">
+      <c r="AJ33">
         <v>11</v>
       </c>
-      <c r="Y33">
+      <c r="AK33">
         <v>512</v>
       </c>
-      <c r="Z33">
+      <c r="AL33">
         <v>99</v>
       </c>
-      <c r="AA33">
+      <c r="AM33">
         <v>147</v>
       </c>
     </row>
-    <row r="34" spans="1:27">
+    <row r="34" spans="1:39">
       <c r="A34" s="1" t="s">
         <v>46</v>
       </c>
@@ -7310,79 +8540,115 @@
         <v>79</v>
       </c>
       <c r="D34">
-        <v>2673</v>
+        <v>62</v>
       </c>
       <c r="E34">
+        <v>589</v>
+      </c>
+      <c r="F34">
+        <v>105</v>
+      </c>
+      <c r="G34">
+        <v>489</v>
+      </c>
+      <c r="H34">
+        <v>673</v>
+      </c>
+      <c r="I34">
+        <v>300</v>
+      </c>
+      <c r="J34">
+        <v>242</v>
+      </c>
+      <c r="K34">
+        <v>213</v>
+      </c>
+      <c r="L34">
         <v>9</v>
       </c>
-      <c r="F34">
+      <c r="M34">
         <v>70</v>
       </c>
-      <c r="G34">
+      <c r="N34">
         <v>28</v>
       </c>
-      <c r="H34">
+      <c r="O34">
         <v>56</v>
       </c>
-      <c r="I34">
-        <v>1273</v>
-      </c>
-      <c r="J34">
+      <c r="P34">
+        <v>195</v>
+      </c>
+      <c r="Q34">
+        <v>704</v>
+      </c>
+      <c r="R34">
+        <v>59</v>
+      </c>
+      <c r="S34">
+        <v>179</v>
+      </c>
+      <c r="T34">
+        <v>32</v>
+      </c>
+      <c r="U34">
+        <v>104</v>
+      </c>
+      <c r="V34">
         <v>2303</v>
       </c>
-      <c r="K34">
+      <c r="W34">
         <v>182</v>
       </c>
-      <c r="L34">
+      <c r="X34">
         <v>105</v>
       </c>
-      <c r="M34">
+      <c r="Y34">
         <v>98</v>
       </c>
-      <c r="N34">
+      <c r="Z34">
         <v>7</v>
       </c>
-      <c r="O34">
+      <c r="AA34">
         <v>15</v>
       </c>
-      <c r="P34">
+      <c r="AB34">
         <v>42</v>
       </c>
-      <c r="Q34">
+      <c r="AC34">
         <v>9</v>
       </c>
-      <c r="R34">
+      <c r="AD34">
         <v>284</v>
       </c>
-      <c r="S34">
+      <c r="AE34">
         <v>91</v>
       </c>
-      <c r="T34">
+      <c r="AF34">
         <v>992</v>
       </c>
-      <c r="U34">
+      <c r="AG34">
         <v>32</v>
       </c>
-      <c r="V34">
+      <c r="AH34">
         <v>515</v>
       </c>
-      <c r="W34">
+      <c r="AI34">
         <v>19</v>
       </c>
-      <c r="X34">
+      <c r="AJ34">
         <v>16</v>
       </c>
-      <c r="Y34">
+      <c r="AK34">
         <v>684</v>
       </c>
-      <c r="Z34">
+      <c r="AL34">
         <v>150</v>
       </c>
-      <c r="AA34">
+      <c r="AM34">
         <v>143</v>
       </c>
     </row>
-    <row r="35" spans="1:27">
+    <row r="35" spans="1:39">
       <c r="A35" s="1" t="s">
         <v>47</v>
       </c>
@@ -7393,79 +8659,115 @@
         <v>10</v>
       </c>
       <c r="D35">
-        <v>1665</v>
+        <v>111</v>
       </c>
       <c r="E35">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F35">
+        <v>79</v>
+      </c>
+      <c r="G35">
+        <v>13</v>
+      </c>
+      <c r="H35">
+        <v>119</v>
+      </c>
+      <c r="I35">
+        <v>14</v>
+      </c>
+      <c r="J35">
+        <v>436</v>
+      </c>
+      <c r="K35">
+        <v>891</v>
+      </c>
+      <c r="L35">
+        <v>1</v>
+      </c>
+      <c r="M35">
         <v>11</v>
       </c>
-      <c r="G35">
+      <c r="N35">
         <v>16</v>
       </c>
-      <c r="H35">
+      <c r="O35">
         <v>5</v>
       </c>
-      <c r="I35">
-        <v>750</v>
-      </c>
-      <c r="J35">
+      <c r="P35">
+        <v>14</v>
+      </c>
+      <c r="Q35">
+        <v>253</v>
+      </c>
+      <c r="R35">
+        <v>152</v>
+      </c>
+      <c r="S35">
+        <v>32</v>
+      </c>
+      <c r="T35">
+        <v>236</v>
+      </c>
+      <c r="U35">
+        <v>63</v>
+      </c>
+      <c r="V35">
         <v>216</v>
       </c>
-      <c r="K35">
+      <c r="W35">
         <v>53</v>
       </c>
-      <c r="L35">
+      <c r="X35">
         <v>11</v>
       </c>
-      <c r="M35">
+      <c r="Y35">
         <v>23</v>
       </c>
-      <c r="N35">
+      <c r="Z35">
         <v>24</v>
       </c>
-      <c r="O35">
+      <c r="AA35">
         <v>61</v>
       </c>
-      <c r="P35">
+      <c r="AB35">
         <v>7</v>
       </c>
-      <c r="Q35">
+      <c r="AC35">
         <v>24</v>
       </c>
-      <c r="R35">
+      <c r="AD35">
         <v>216</v>
       </c>
-      <c r="S35">
+      <c r="AE35">
         <v>31</v>
       </c>
-      <c r="T35">
+      <c r="AF35">
         <v>137</v>
       </c>
-      <c r="U35">
+      <c r="AG35">
         <v>58</v>
       </c>
-      <c r="V35">
+      <c r="AH35">
         <v>264</v>
       </c>
-      <c r="W35">
+      <c r="AI35">
         <v>7</v>
       </c>
-      <c r="X35">
+      <c r="AJ35">
         <v>3</v>
       </c>
-      <c r="Y35">
+      <c r="AK35">
         <v>4256</v>
       </c>
-      <c r="Z35">
+      <c r="AL35">
         <v>354</v>
       </c>
-      <c r="AA35">
+      <c r="AM35">
         <v>667</v>
       </c>
     </row>
-    <row r="36" spans="1:27">
+    <row r="36" spans="1:39">
       <c r="A36" s="1" t="s">
         <v>48</v>
       </c>
@@ -7476,79 +8778,115 @@
         <v>6</v>
       </c>
       <c r="D36">
-        <v>1741</v>
+        <v>44</v>
       </c>
       <c r="E36">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F36">
+        <v>163</v>
+      </c>
+      <c r="G36">
+        <v>16</v>
+      </c>
+      <c r="H36">
+        <v>38</v>
+      </c>
+      <c r="I36">
+        <v>2</v>
+      </c>
+      <c r="J36">
+        <v>301</v>
+      </c>
+      <c r="K36">
+        <v>1159</v>
+      </c>
+      <c r="L36">
+        <v>0</v>
+      </c>
+      <c r="M36">
         <v>6</v>
       </c>
-      <c r="G36">
-        <v>1</v>
-      </c>
-      <c r="H36">
+      <c r="N36">
+        <v>1</v>
+      </c>
+      <c r="O36">
         <v>8</v>
       </c>
-      <c r="I36">
-        <v>653</v>
-      </c>
-      <c r="J36">
+      <c r="P36">
+        <v>0</v>
+      </c>
+      <c r="Q36">
+        <v>164</v>
+      </c>
+      <c r="R36">
+        <v>269</v>
+      </c>
+      <c r="S36">
+        <v>40</v>
+      </c>
+      <c r="T36">
+        <v>114</v>
+      </c>
+      <c r="U36">
+        <v>66</v>
+      </c>
+      <c r="V36">
         <v>434</v>
       </c>
-      <c r="K36">
+      <c r="W36">
         <v>51</v>
       </c>
-      <c r="L36">
+      <c r="X36">
         <v>3</v>
       </c>
-      <c r="M36">
+      <c r="Y36">
         <v>17</v>
       </c>
-      <c r="N36">
+      <c r="Z36">
         <v>24</v>
       </c>
-      <c r="O36">
+      <c r="AA36">
         <v>88</v>
       </c>
-      <c r="P36">
+      <c r="AB36">
         <v>2</v>
       </c>
-      <c r="Q36">
+      <c r="AC36">
         <v>25</v>
       </c>
-      <c r="R36">
+      <c r="AD36">
         <v>144</v>
       </c>
-      <c r="S36">
+      <c r="AE36">
         <v>5</v>
       </c>
-      <c r="T36">
+      <c r="AF36">
         <v>24</v>
       </c>
-      <c r="U36">
+      <c r="AG36">
         <v>14</v>
       </c>
-      <c r="V36">
+      <c r="AH36">
         <v>110</v>
       </c>
-      <c r="W36">
+      <c r="AI36">
         <v>19</v>
       </c>
-      <c r="X36">
-        <v>0</v>
-      </c>
-      <c r="Y36">
+      <c r="AJ36">
+        <v>0</v>
+      </c>
+      <c r="AK36">
         <v>7141</v>
       </c>
-      <c r="Z36">
+      <c r="AL36">
         <v>649</v>
       </c>
-      <c r="AA36">
+      <c r="AM36">
         <v>519</v>
       </c>
     </row>
-    <row r="37" spans="1:27">
+    <row r="37" spans="1:39">
       <c r="A37" s="1" t="s">
         <v>49</v>
       </c>
@@ -7559,79 +8897,115 @@
         <v>1</v>
       </c>
       <c r="D37">
-        <v>1000</v>
+        <v>71</v>
       </c>
       <c r="E37">
+        <v>161</v>
+      </c>
+      <c r="F37">
+        <v>10</v>
+      </c>
+      <c r="G37">
+        <v>79</v>
+      </c>
+      <c r="H37">
+        <v>12</v>
+      </c>
+      <c r="I37">
+        <v>53</v>
+      </c>
+      <c r="J37">
+        <v>223</v>
+      </c>
+      <c r="K37">
+        <v>391</v>
+      </c>
+      <c r="L37">
         <v>3</v>
       </c>
-      <c r="F37">
+      <c r="M37">
         <v>17</v>
       </c>
-      <c r="G37">
-        <v>1</v>
-      </c>
-      <c r="H37">
+      <c r="N37">
+        <v>1</v>
+      </c>
+      <c r="O37">
         <v>11</v>
-      </c>
-      <c r="I37">
-        <v>1051</v>
-      </c>
-      <c r="J37">
-        <v>2217</v>
-      </c>
-      <c r="K37">
-        <v>5</v>
-      </c>
-      <c r="L37">
-        <v>56</v>
-      </c>
-      <c r="M37">
-        <v>15</v>
-      </c>
-      <c r="N37">
-        <v>5</v>
-      </c>
-      <c r="O37">
-        <v>15</v>
       </c>
       <c r="P37">
         <v>10</v>
       </c>
       <c r="Q37">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="R37">
+        <v>419</v>
+      </c>
+      <c r="S37">
+        <v>266</v>
+      </c>
+      <c r="T37">
+        <v>149</v>
+      </c>
+      <c r="U37">
+        <v>166</v>
+      </c>
+      <c r="V37">
+        <v>2217</v>
+      </c>
+      <c r="W37">
+        <v>5</v>
+      </c>
+      <c r="X37">
+        <v>56</v>
+      </c>
+      <c r="Y37">
+        <v>15</v>
+      </c>
+      <c r="Z37">
+        <v>5</v>
+      </c>
+      <c r="AA37">
+        <v>15</v>
+      </c>
+      <c r="AB37">
+        <v>10</v>
+      </c>
+      <c r="AC37">
+        <v>0</v>
+      </c>
+      <c r="AD37">
         <v>465</v>
       </c>
-      <c r="S37">
-        <v>1</v>
-      </c>
-      <c r="T37">
+      <c r="AE37">
+        <v>1</v>
+      </c>
+      <c r="AF37">
         <v>298</v>
       </c>
-      <c r="U37">
+      <c r="AG37">
         <v>9</v>
       </c>
-      <c r="V37">
+      <c r="AH37">
         <v>301</v>
       </c>
-      <c r="W37">
-        <v>0</v>
-      </c>
-      <c r="X37">
+      <c r="AI37">
+        <v>0</v>
+      </c>
+      <c r="AJ37">
         <v>5</v>
       </c>
-      <c r="Y37">
+      <c r="AK37">
         <v>5711</v>
       </c>
-      <c r="Z37">
+      <c r="AL37">
         <v>362</v>
       </c>
-      <c r="AA37">
+      <c r="AM37">
         <v>11</v>
       </c>
     </row>
-    <row r="38" spans="1:27">
+    <row r="38" spans="1:39">
       <c r="A38" s="1" t="s">
         <v>50</v>
       </c>
@@ -7642,79 +9016,115 @@
         <v>3</v>
       </c>
       <c r="D38">
-        <v>408</v>
+        <v>23</v>
       </c>
       <c r="E38">
-        <v>1</v>
+        <v>324</v>
       </c>
       <c r="F38">
+        <v>7</v>
+      </c>
+      <c r="G38">
+        <v>20</v>
+      </c>
+      <c r="H38">
+        <v>7</v>
+      </c>
+      <c r="I38">
+        <v>9</v>
+      </c>
+      <c r="J38">
+        <v>5</v>
+      </c>
+      <c r="K38">
+        <v>13</v>
+      </c>
+      <c r="L38">
+        <v>1</v>
+      </c>
+      <c r="M38">
         <v>54</v>
-      </c>
-      <c r="G38">
-        <v>2</v>
-      </c>
-      <c r="H38">
-        <v>20</v>
-      </c>
-      <c r="I38">
-        <v>772</v>
-      </c>
-      <c r="J38">
-        <v>852</v>
-      </c>
-      <c r="K38">
-        <v>4</v>
-      </c>
-      <c r="L38">
-        <v>38</v>
-      </c>
-      <c r="M38">
-        <v>1</v>
       </c>
       <c r="N38">
         <v>2</v>
       </c>
       <c r="O38">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="P38">
+        <v>0</v>
+      </c>
+      <c r="Q38">
+        <v>25</v>
+      </c>
+      <c r="R38">
+        <v>253</v>
+      </c>
+      <c r="S38">
+        <v>305</v>
+      </c>
+      <c r="T38">
+        <v>36</v>
+      </c>
+      <c r="U38">
+        <v>153</v>
+      </c>
+      <c r="V38">
+        <v>852</v>
+      </c>
+      <c r="W38">
+        <v>4</v>
+      </c>
+      <c r="X38">
+        <v>38</v>
+      </c>
+      <c r="Y38">
+        <v>1</v>
+      </c>
+      <c r="Z38">
         <v>2</v>
       </c>
-      <c r="Q38">
-        <v>0</v>
-      </c>
-      <c r="R38">
+      <c r="AA38">
+        <v>0</v>
+      </c>
+      <c r="AB38">
+        <v>2</v>
+      </c>
+      <c r="AC38">
+        <v>0</v>
+      </c>
+      <c r="AD38">
         <v>133</v>
       </c>
-      <c r="S38">
-        <v>0</v>
-      </c>
-      <c r="T38">
+      <c r="AE38">
+        <v>0</v>
+      </c>
+      <c r="AF38">
         <v>1395</v>
       </c>
-      <c r="U38">
+      <c r="AG38">
         <v>45</v>
       </c>
-      <c r="V38">
+      <c r="AH38">
         <v>36</v>
       </c>
-      <c r="W38">
+      <c r="AI38">
         <v>15</v>
       </c>
-      <c r="X38">
+      <c r="AJ38">
         <v>12</v>
       </c>
-      <c r="Y38">
+      <c r="AK38">
         <v>1354</v>
       </c>
-      <c r="Z38">
+      <c r="AL38">
         <v>73</v>
       </c>
-      <c r="AA38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:27">
+      <c r="AM38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:39">
       <c r="A39" s="1" t="s">
         <v>51</v>
       </c>
@@ -7725,79 +9135,115 @@
         <v>0</v>
       </c>
       <c r="D39">
-        <v>969</v>
+        <v>8</v>
       </c>
       <c r="E39">
-        <v>2</v>
+        <v>727</v>
       </c>
       <c r="F39">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="G39">
-        <v>2</v>
+        <v>123</v>
       </c>
       <c r="H39">
         <v>20</v>
       </c>
       <c r="I39">
-        <v>336</v>
+        <v>8</v>
       </c>
       <c r="J39">
+        <v>2</v>
+      </c>
+      <c r="K39">
+        <v>24</v>
+      </c>
+      <c r="L39">
+        <v>2</v>
+      </c>
+      <c r="M39">
+        <v>23</v>
+      </c>
+      <c r="N39">
+        <v>2</v>
+      </c>
+      <c r="O39">
+        <v>20</v>
+      </c>
+      <c r="P39">
+        <v>102</v>
+      </c>
+      <c r="Q39">
+        <v>13</v>
+      </c>
+      <c r="R39">
+        <v>63</v>
+      </c>
+      <c r="S39">
+        <v>106</v>
+      </c>
+      <c r="T39">
+        <v>5</v>
+      </c>
+      <c r="U39">
+        <v>47</v>
+      </c>
+      <c r="V39">
         <v>3184</v>
       </c>
-      <c r="K39">
+      <c r="W39">
         <v>7</v>
       </c>
-      <c r="L39">
+      <c r="X39">
         <v>37</v>
       </c>
-      <c r="M39">
+      <c r="Y39">
         <v>17</v>
       </c>
-      <c r="N39">
-        <v>0</v>
-      </c>
-      <c r="O39">
-        <v>0</v>
-      </c>
-      <c r="P39">
+      <c r="Z39">
+        <v>0</v>
+      </c>
+      <c r="AA39">
+        <v>0</v>
+      </c>
+      <c r="AB39">
         <v>4</v>
       </c>
-      <c r="Q39">
+      <c r="AC39">
         <v>2</v>
       </c>
-      <c r="R39">
+      <c r="AD39">
         <v>17</v>
       </c>
-      <c r="S39">
+      <c r="AE39">
         <v>9</v>
       </c>
-      <c r="T39">
+      <c r="AF39">
         <v>1029</v>
       </c>
-      <c r="U39">
+      <c r="AG39">
         <v>12</v>
       </c>
-      <c r="V39">
+      <c r="AH39">
         <v>42</v>
       </c>
-      <c r="W39">
+      <c r="AI39">
         <v>16</v>
       </c>
-      <c r="X39">
+      <c r="AJ39">
         <v>498</v>
       </c>
-      <c r="Y39">
+      <c r="AK39">
         <v>163</v>
       </c>
-      <c r="Z39">
+      <c r="AL39">
         <v>309</v>
       </c>
-      <c r="AA39">
+      <c r="AM39">
         <v>18</v>
       </c>
     </row>
-    <row r="40" spans="1:27">
+    <row r="40" spans="1:39">
       <c r="A40" s="1" t="s">
         <v>52</v>
       </c>
@@ -7808,79 +9254,115 @@
         <v>245</v>
       </c>
       <c r="D40">
-        <v>1555</v>
+        <v>347</v>
       </c>
       <c r="E40">
+        <v>29</v>
+      </c>
+      <c r="F40">
+        <v>130</v>
+      </c>
+      <c r="G40">
+        <v>158</v>
+      </c>
+      <c r="H40">
+        <v>190</v>
+      </c>
+      <c r="I40">
+        <v>70</v>
+      </c>
+      <c r="J40">
+        <v>467</v>
+      </c>
+      <c r="K40">
+        <v>164</v>
+      </c>
+      <c r="L40">
         <v>98</v>
       </c>
-      <c r="F40">
+      <c r="M40">
         <v>634</v>
       </c>
-      <c r="G40">
+      <c r="N40">
         <v>354</v>
       </c>
-      <c r="H40">
+      <c r="O40">
         <v>102</v>
       </c>
-      <c r="I40">
-        <v>457</v>
-      </c>
-      <c r="J40">
+      <c r="P40">
+        <v>9</v>
+      </c>
+      <c r="Q40">
+        <v>55</v>
+      </c>
+      <c r="R40">
+        <v>129</v>
+      </c>
+      <c r="S40">
+        <v>136</v>
+      </c>
+      <c r="T40">
+        <v>66</v>
+      </c>
+      <c r="U40">
+        <v>62</v>
+      </c>
+      <c r="V40">
         <v>474</v>
       </c>
-      <c r="K40">
+      <c r="W40">
         <v>73</v>
       </c>
-      <c r="L40">
+      <c r="X40">
         <v>65</v>
       </c>
-      <c r="M40">
+      <c r="Y40">
         <v>110</v>
       </c>
-      <c r="N40">
+      <c r="Z40">
         <v>172</v>
       </c>
-      <c r="O40">
+      <c r="AA40">
         <v>354</v>
       </c>
-      <c r="P40">
+      <c r="AB40">
         <v>69</v>
       </c>
-      <c r="Q40">
+      <c r="AC40">
         <v>163</v>
       </c>
-      <c r="R40">
+      <c r="AD40">
         <v>126</v>
       </c>
-      <c r="S40">
+      <c r="AE40">
         <v>98</v>
       </c>
-      <c r="T40">
+      <c r="AF40">
         <v>8</v>
       </c>
-      <c r="U40">
+      <c r="AG40">
         <v>21</v>
       </c>
-      <c r="V40">
+      <c r="AH40">
         <v>1378</v>
       </c>
-      <c r="W40">
+      <c r="AI40">
         <v>8</v>
       </c>
-      <c r="X40">
-        <v>0</v>
-      </c>
-      <c r="Y40">
+      <c r="AJ40">
+        <v>0</v>
+      </c>
+      <c r="AK40">
         <v>1525</v>
       </c>
-      <c r="Z40">
+      <c r="AL40">
         <v>27</v>
       </c>
-      <c r="AA40">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:27">
+      <c r="AM40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:39">
       <c r="A41" s="1" t="s">
         <v>53</v>
       </c>
@@ -7891,79 +9373,115 @@
         <v>130</v>
       </c>
       <c r="D41">
-        <v>1041</v>
+        <v>13</v>
       </c>
       <c r="E41">
+        <v>117</v>
+      </c>
+      <c r="F41">
+        <v>131</v>
+      </c>
+      <c r="G41">
+        <v>232</v>
+      </c>
+      <c r="H41">
+        <v>37</v>
+      </c>
+      <c r="I41">
+        <v>106</v>
+      </c>
+      <c r="J41">
+        <v>344</v>
+      </c>
+      <c r="K41">
+        <v>61</v>
+      </c>
+      <c r="L41">
         <v>57</v>
       </c>
-      <c r="F41">
+      <c r="M41">
         <v>585</v>
       </c>
-      <c r="G41">
+      <c r="N41">
         <v>129</v>
       </c>
-      <c r="H41">
+      <c r="O41">
         <v>119</v>
       </c>
-      <c r="I41">
-        <v>374</v>
-      </c>
-      <c r="J41">
+      <c r="P41">
+        <v>26</v>
+      </c>
+      <c r="Q41">
+        <v>45</v>
+      </c>
+      <c r="R41">
+        <v>76</v>
+      </c>
+      <c r="S41">
+        <v>139</v>
+      </c>
+      <c r="T41">
+        <v>30</v>
+      </c>
+      <c r="U41">
+        <v>58</v>
+      </c>
+      <c r="V41">
         <v>7</v>
       </c>
-      <c r="K41">
+      <c r="W41">
         <v>68</v>
       </c>
-      <c r="L41">
+      <c r="X41">
         <v>7</v>
       </c>
-      <c r="M41">
+      <c r="Y41">
         <v>128</v>
       </c>
-      <c r="N41">
+      <c r="Z41">
         <v>74</v>
       </c>
-      <c r="O41">
+      <c r="AA41">
         <v>4</v>
       </c>
-      <c r="P41">
+      <c r="AB41">
         <v>22</v>
       </c>
-      <c r="Q41">
+      <c r="AC41">
         <v>2</v>
       </c>
-      <c r="R41">
+      <c r="AD41">
         <v>108</v>
       </c>
-      <c r="S41">
+      <c r="AE41">
         <v>208</v>
       </c>
-      <c r="T41">
+      <c r="AF41">
         <v>90</v>
       </c>
-      <c r="U41">
+      <c r="AG41">
         <v>43</v>
       </c>
-      <c r="V41">
-        <v>0</v>
-      </c>
-      <c r="W41">
-        <v>0</v>
-      </c>
-      <c r="X41">
+      <c r="AH41">
+        <v>0</v>
+      </c>
+      <c r="AI41">
+        <v>0</v>
+      </c>
+      <c r="AJ41">
         <v>8</v>
       </c>
-      <c r="Y41">
-        <v>0</v>
-      </c>
-      <c r="Z41">
-        <v>0</v>
-      </c>
-      <c r="AA41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:27">
+      <c r="AK41">
+        <v>0</v>
+      </c>
+      <c r="AL41">
+        <v>0</v>
+      </c>
+      <c r="AM41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:39">
       <c r="A42" s="1" t="s">
         <v>54</v>
       </c>
@@ -7974,75 +9492,111 @@
         <v>2954</v>
       </c>
       <c r="D42">
-        <v>47964</v>
+        <v>8489</v>
       </c>
       <c r="E42">
+        <v>6457</v>
+      </c>
+      <c r="F42">
+        <v>2935</v>
+      </c>
+      <c r="G42">
+        <v>7914</v>
+      </c>
+      <c r="H42">
+        <v>3076</v>
+      </c>
+      <c r="I42">
+        <v>7569</v>
+      </c>
+      <c r="J42">
+        <v>5840</v>
+      </c>
+      <c r="K42">
+        <v>5684</v>
+      </c>
+      <c r="L42">
         <v>1542</v>
       </c>
-      <c r="F42">
+      <c r="M42">
         <v>9453</v>
       </c>
-      <c r="G42">
+      <c r="N42">
         <v>2385</v>
       </c>
-      <c r="H42">
+      <c r="O42">
         <v>5392</v>
       </c>
-      <c r="I42">
-        <v>33800</v>
-      </c>
-      <c r="J42">
+      <c r="P42">
+        <v>1732</v>
+      </c>
+      <c r="Q42">
+        <v>3611</v>
+      </c>
+      <c r="R42">
+        <v>7307</v>
+      </c>
+      <c r="S42">
+        <v>13011</v>
+      </c>
+      <c r="T42">
+        <v>2381</v>
+      </c>
+      <c r="U42">
+        <v>5758</v>
+      </c>
+      <c r="V42">
         <v>28415</v>
       </c>
-      <c r="K42">
+      <c r="W42">
         <v>3091</v>
       </c>
-      <c r="L42">
+      <c r="X42">
         <v>2637</v>
       </c>
-      <c r="M42">
+      <c r="Y42">
         <v>2519</v>
       </c>
-      <c r="N42">
+      <c r="Z42">
         <v>1764</v>
       </c>
-      <c r="O42">
+      <c r="AA42">
         <v>5291</v>
       </c>
-      <c r="P42">
+      <c r="AB42">
         <v>1164</v>
       </c>
-      <c r="Q42">
+      <c r="AC42">
         <v>2578</v>
       </c>
-      <c r="R42">
+      <c r="AD42">
         <v>7508</v>
       </c>
-      <c r="S42">
+      <c r="AE42">
         <v>2822</v>
       </c>
-      <c r="T42">
+      <c r="AF42">
         <v>20449</v>
       </c>
-      <c r="U42">
+      <c r="AG42">
         <v>1193</v>
       </c>
-      <c r="V42">
+      <c r="AH42">
         <v>10975</v>
       </c>
-      <c r="W42">
+      <c r="AI42">
         <v>4158</v>
       </c>
-      <c r="X42">
+      <c r="AJ42">
         <v>2732</v>
       </c>
-      <c r="Y42">
+      <c r="AK42">
         <v>30900</v>
       </c>
-      <c r="Z42">
+      <c r="AL42">
         <v>11408</v>
       </c>
-      <c r="AA42">
+      <c r="AM42">
         <v>5033</v>
       </c>
     </row>
